--- a/cirt_data.xlsx
+++ b/cirt_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu-my.sharepoint.com/personal/daad2295_colorado_edu/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce1ebde9cded71ae/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1429" documentId="13_ncr:1_{C6350078-5CFC-4B20-8D31-D68148B331D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D338404A-8BB8-41F7-A7DF-F030CB048AA9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DEE3B3B-C278-45E7-AFEB-FC7D865F8C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{969D6A76-162A-4286-A653-6BBA36AECB0D}"/>
   </bookViews>
@@ -17,8 +17,8 @@
     <sheet name="topics" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">courses!$A$1:$R$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">topics!$A$1:$T$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">courses!$A$1:$S$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">topics!$A$1:$U$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10208" uniqueCount="2750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11091" uniqueCount="2751">
   <si>
     <t>Effective Communication: Writing</t>
   </si>
@@ -8288,6 +8288,9 @@
   </si>
   <si>
     <t>Since CSCI 5809 and ATLS 5809 are cross-listed, ATLS 5809 does not count against non-CS course limit. However,  ATLS 5809 may have additional registration restrictions.</t>
+  </si>
+  <si>
+    <t>rigor</t>
   </si>
 </sst>
 </file>
@@ -8859,10 +8862,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -9180,19 +9179,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A57DF34-4FD0-476A-ABD4-C75283F5DBFA}">
-  <dimension ref="A1:R440"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S440"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="11.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" style="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" style="2" customWidth="1"/>
-    <col min="6" max="15" width="14.7109375" style="1" customWidth="1"/>
-    <col min="16" max="25" width="14.85546875" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.81640625" style="2" customWidth="1"/>
+    <col min="6" max="15" width="14.7265625" style="1" customWidth="1"/>
+    <col min="16" max="25" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>300</v>
       </c>
@@ -9247,8 +9246,11 @@
       <c r="R1" s="1" t="s">
         <v>2687</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S1" s="1" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>319</v>
       </c>
@@ -9303,8 +9305,11 @@
       <c r="R2" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S2" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>325</v>
       </c>
@@ -9359,8 +9364,11 @@
       <c r="R3" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S3" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>329</v>
       </c>
@@ -9415,8 +9423,11 @@
       <c r="R4" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S4" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>335</v>
       </c>
@@ -9471,8 +9482,11 @@
       <c r="R5" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S5" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>341</v>
       </c>
@@ -9527,8 +9541,11 @@
       <c r="R6" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S6" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>346</v>
       </c>
@@ -9583,8 +9600,11 @@
       <c r="R7" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S7" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>352</v>
       </c>
@@ -9639,8 +9659,11 @@
       <c r="R8" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S8" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>358</v>
       </c>
@@ -9695,8 +9718,11 @@
       <c r="R9" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S9" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>363</v>
       </c>
@@ -9751,8 +9777,11 @@
       <c r="R10" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S10" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>368</v>
       </c>
@@ -9807,8 +9836,11 @@
       <c r="R11" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S11" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>373</v>
       </c>
@@ -9863,8 +9895,11 @@
       <c r="R12" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S12" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>377</v>
       </c>
@@ -9919,8 +9954,11 @@
       <c r="R13" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S13" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>383</v>
       </c>
@@ -9975,8 +10013,11 @@
       <c r="R14" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S14" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>388</v>
       </c>
@@ -10031,8 +10072,11 @@
       <c r="R15" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S15" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>393</v>
       </c>
@@ -10087,8 +10131,11 @@
       <c r="R16" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S16" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>398</v>
       </c>
@@ -10143,8 +10190,11 @@
       <c r="R17" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S17" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>402</v>
       </c>
@@ -10199,8 +10249,11 @@
       <c r="R18" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S18" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>407</v>
       </c>
@@ -10255,8 +10308,11 @@
       <c r="R19" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S19" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>412</v>
       </c>
@@ -10311,8 +10367,11 @@
       <c r="R20" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S20" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="1" t="s">
         <v>416</v>
       </c>
@@ -10367,8 +10426,11 @@
       <c r="R21" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S21" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="1" t="s">
         <v>421</v>
       </c>
@@ -10423,8 +10485,11 @@
       <c r="R22" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S22" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="1" t="s">
         <v>425</v>
       </c>
@@ -10479,8 +10544,11 @@
       <c r="R23" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S23" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="1" t="s">
         <v>431</v>
       </c>
@@ -10535,8 +10603,11 @@
       <c r="R24" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S24" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
         <v>436</v>
       </c>
@@ -10591,8 +10662,11 @@
       <c r="R25" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S25" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="1" t="s">
         <v>441</v>
       </c>
@@ -10647,8 +10721,11 @@
       <c r="R26" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S26" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
         <v>446</v>
       </c>
@@ -10703,8 +10780,11 @@
       <c r="R27" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S27" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="1" t="s">
         <v>452</v>
       </c>
@@ -10759,8 +10839,11 @@
       <c r="R28" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S28" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="1" t="s">
         <v>457</v>
       </c>
@@ -10815,8 +10898,11 @@
       <c r="R29" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S29" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
         <v>462</v>
       </c>
@@ -10871,8 +10957,11 @@
       <c r="R30" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S30" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="1" t="s">
         <v>466</v>
       </c>
@@ -10927,8 +11016,11 @@
       <c r="R31" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S31" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="1" t="s">
         <v>471</v>
       </c>
@@ -10983,8 +11075,11 @@
       <c r="R32" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S32" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="1" t="s">
         <v>476</v>
       </c>
@@ -11039,8 +11134,11 @@
       <c r="R33" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S33" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="1" t="s">
         <v>481</v>
       </c>
@@ -11095,8 +11193,11 @@
       <c r="R34" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S34" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="1" t="s">
         <v>486</v>
       </c>
@@ -11151,8 +11252,11 @@
       <c r="R35" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S35" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="1" t="s">
         <v>490</v>
       </c>
@@ -11207,8 +11311,11 @@
       <c r="R36" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S36" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="1" t="s">
         <v>494</v>
       </c>
@@ -11263,8 +11370,11 @@
       <c r="R37" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S37" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="1" t="s">
         <v>498</v>
       </c>
@@ -11319,8 +11429,11 @@
       <c r="R38" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S38" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="1" t="s">
         <v>502</v>
       </c>
@@ -11375,8 +11488,11 @@
       <c r="R39" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S39" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="1" t="s">
         <v>506</v>
       </c>
@@ -11431,8 +11547,11 @@
       <c r="R40" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S40" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="1" t="s">
         <v>510</v>
       </c>
@@ -11487,8 +11606,11 @@
       <c r="R41" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S41" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>514</v>
       </c>
@@ -11543,8 +11665,11 @@
       <c r="R42" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S42" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>518</v>
       </c>
@@ -11599,8 +11724,11 @@
       <c r="R43" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S43" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>522</v>
       </c>
@@ -11655,8 +11783,11 @@
       <c r="R44" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S44" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="1" t="s">
         <v>526</v>
       </c>
@@ -11711,8 +11842,11 @@
       <c r="R45" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S45" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="1" t="s">
         <v>530</v>
       </c>
@@ -11767,8 +11901,11 @@
       <c r="R46" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S46" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="1" t="s">
         <v>534</v>
       </c>
@@ -11823,8 +11960,11 @@
       <c r="R47" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S47" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="1" t="s">
         <v>538</v>
       </c>
@@ -11879,8 +12019,11 @@
       <c r="R48" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S48" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>542</v>
       </c>
@@ -11935,8 +12078,11 @@
       <c r="R49" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S49" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>548</v>
       </c>
@@ -11991,8 +12137,11 @@
       <c r="R50" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S50" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>552</v>
       </c>
@@ -12047,8 +12196,11 @@
       <c r="R51" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S51" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>557</v>
       </c>
@@ -12103,8 +12255,11 @@
       <c r="R52" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S52" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>561</v>
       </c>
@@ -12159,8 +12314,11 @@
       <c r="R53" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S53" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
         <v>565</v>
       </c>
@@ -12215,8 +12373,11 @@
       <c r="R54" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S54" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" s="1" t="s">
         <v>569</v>
       </c>
@@ -12271,8 +12432,11 @@
       <c r="R55" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S55" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" s="1" t="s">
         <v>574</v>
       </c>
@@ -12327,8 +12491,11 @@
       <c r="R56" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S56" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" s="1" t="s">
         <v>578</v>
       </c>
@@ -12383,8 +12550,11 @@
       <c r="R57" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S57" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" s="1" t="s">
         <v>582</v>
       </c>
@@ -12439,8 +12609,11 @@
       <c r="R58" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S58" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" s="1" t="s">
         <v>587</v>
       </c>
@@ -12495,8 +12668,11 @@
       <c r="R59" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S59" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" s="1" t="s">
         <v>593</v>
       </c>
@@ -12551,8 +12727,11 @@
       <c r="R60" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S60" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" s="1" t="s">
         <v>598</v>
       </c>
@@ -12607,8 +12786,11 @@
       <c r="R61" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S61" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" s="1" t="s">
         <v>602</v>
       </c>
@@ -12663,8 +12845,11 @@
       <c r="R62" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S62" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" s="1" t="s">
         <v>606</v>
       </c>
@@ -12719,8 +12904,11 @@
       <c r="R63" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S63" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
         <v>610</v>
       </c>
@@ -12775,8 +12963,11 @@
       <c r="R64" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S64" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
         <v>614</v>
       </c>
@@ -12831,8 +13022,11 @@
       <c r="R65" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S65" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" s="1" t="s">
         <v>620</v>
       </c>
@@ -12887,8 +13081,11 @@
       <c r="R66" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S66" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
         <v>624</v>
       </c>
@@ -12943,8 +13140,11 @@
       <c r="R67" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S67" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
         <v>628</v>
       </c>
@@ -12999,8 +13199,11 @@
       <c r="R68" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S68" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
         <v>632</v>
       </c>
@@ -13055,8 +13258,11 @@
       <c r="R69" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S69" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
         <v>636</v>
       </c>
@@ -13111,8 +13317,11 @@
       <c r="R70" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S70" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
         <v>640</v>
       </c>
@@ -13167,8 +13376,11 @@
       <c r="R71" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S71" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
         <v>644</v>
       </c>
@@ -13223,8 +13435,11 @@
       <c r="R72" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S72" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
         <v>648</v>
       </c>
@@ -13279,8 +13494,11 @@
       <c r="R73" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S73" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
         <v>652</v>
       </c>
@@ -13335,8 +13553,11 @@
       <c r="R74" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S74" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" s="1" t="s">
         <v>656</v>
       </c>
@@ -13391,8 +13612,11 @@
       <c r="R75" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S75" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
         <v>660</v>
       </c>
@@ -13447,8 +13671,11 @@
       <c r="R76" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S76" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
         <v>664</v>
       </c>
@@ -13503,8 +13730,11 @@
       <c r="R77" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S77" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" s="1" t="s">
         <v>668</v>
       </c>
@@ -13559,8 +13789,11 @@
       <c r="R78" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S78" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
         <v>672</v>
       </c>
@@ -13615,8 +13848,11 @@
       <c r="R79" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S79" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
         <v>676</v>
       </c>
@@ -13671,8 +13907,11 @@
       <c r="R80" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S80" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
         <v>680</v>
       </c>
@@ -13727,8 +13966,11 @@
       <c r="R81" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S81" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
         <v>684</v>
       </c>
@@ -13783,8 +14025,11 @@
       <c r="R82" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S82" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
         <v>688</v>
       </c>
@@ -13839,8 +14084,11 @@
       <c r="R83" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S83" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" s="1" t="s">
         <v>692</v>
       </c>
@@ -13895,8 +14143,11 @@
       <c r="R84" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S84" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
         <v>696</v>
       </c>
@@ -13951,8 +14202,11 @@
       <c r="R85" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S85" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
         <v>700</v>
       </c>
@@ -14007,8 +14261,11 @@
       <c r="R86" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S86" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
         <v>704</v>
       </c>
@@ -14063,8 +14320,11 @@
       <c r="R87" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S87" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
         <v>708</v>
       </c>
@@ -14119,8 +14379,11 @@
       <c r="R88" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S88" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
         <v>712</v>
       </c>
@@ -14175,8 +14438,11 @@
       <c r="R89" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S89" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" s="1" t="s">
         <v>716</v>
       </c>
@@ -14231,8 +14497,11 @@
       <c r="R90" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S90" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
         <v>720</v>
       </c>
@@ -14287,8 +14556,11 @@
       <c r="R91" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S91" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
         <v>724</v>
       </c>
@@ -14343,8 +14615,11 @@
       <c r="R92" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S92" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
         <v>728</v>
       </c>
@@ -14399,8 +14674,11 @@
       <c r="R93" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S93" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
         <v>732</v>
       </c>
@@ -14455,8 +14733,11 @@
       <c r="R94" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S94" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
         <v>736</v>
       </c>
@@ -14511,8 +14792,11 @@
       <c r="R95" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S95" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
         <v>740</v>
       </c>
@@ -14567,8 +14851,11 @@
       <c r="R96" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S96" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
         <v>744</v>
       </c>
@@ -14623,8 +14910,11 @@
       <c r="R97" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S97" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
         <v>748</v>
       </c>
@@ -14679,8 +14969,11 @@
       <c r="R98" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S98" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
         <v>752</v>
       </c>
@@ -14735,8 +15028,11 @@
       <c r="R99" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S99" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>756</v>
       </c>
@@ -14791,8 +15087,11 @@
       <c r="R100" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S100" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101" s="1" t="s">
         <v>760</v>
       </c>
@@ -14847,8 +15146,11 @@
       <c r="R101" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S101" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
         <v>764</v>
       </c>
@@ -14903,8 +15205,11 @@
       <c r="R102" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S102" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
         <v>768</v>
       </c>
@@ -14959,8 +15264,11 @@
       <c r="R103" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S103" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104" s="1" t="s">
         <v>772</v>
       </c>
@@ -15015,8 +15323,11 @@
       <c r="R104" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S104" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
         <v>776</v>
       </c>
@@ -15071,8 +15382,11 @@
       <c r="R105" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S105" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106" s="1" t="s">
         <v>780</v>
       </c>
@@ -15127,8 +15441,11 @@
       <c r="R106" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S106" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>784</v>
       </c>
@@ -15183,8 +15500,11 @@
       <c r="R107" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S107" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108" s="1" t="s">
         <v>788</v>
       </c>
@@ -15239,8 +15559,11 @@
       <c r="R108" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S108" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
         <v>792</v>
       </c>
@@ -15295,8 +15618,11 @@
       <c r="R109" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S109" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
         <v>796</v>
       </c>
@@ -15351,8 +15677,11 @@
       <c r="R110" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S110" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
         <v>800</v>
       </c>
@@ -15407,8 +15736,11 @@
       <c r="R111" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S111" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
         <v>804</v>
       </c>
@@ -15463,8 +15795,11 @@
       <c r="R112" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S112" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113" s="1" t="s">
         <v>808</v>
       </c>
@@ -15519,8 +15854,11 @@
       <c r="R113" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S113" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
         <v>812</v>
       </c>
@@ -15575,8 +15913,11 @@
       <c r="R114" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S114" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
         <v>816</v>
       </c>
@@ -15631,8 +15972,11 @@
       <c r="R115" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S115" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
         <v>820</v>
       </c>
@@ -15687,8 +16031,11 @@
       <c r="R116" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S116" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
         <v>824</v>
       </c>
@@ -15743,8 +16090,11 @@
       <c r="R117" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S117" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118" s="1" t="s">
         <v>828</v>
       </c>
@@ -15799,8 +16149,11 @@
       <c r="R118" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S118" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119" s="1" t="s">
         <v>832</v>
       </c>
@@ -15855,8 +16208,11 @@
       <c r="R119" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S119" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120" s="1" t="s">
         <v>836</v>
       </c>
@@ -15911,8 +16267,11 @@
       <c r="R120" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S120" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
         <v>840</v>
       </c>
@@ -15967,8 +16326,11 @@
       <c r="R121" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S121" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
         <v>844</v>
       </c>
@@ -16023,8 +16385,11 @@
       <c r="R122" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S122" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
         <v>847</v>
       </c>
@@ -16079,8 +16444,11 @@
       <c r="R123" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S123" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
         <v>851</v>
       </c>
@@ -16135,8 +16503,11 @@
       <c r="R124" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S124" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125" s="1" t="s">
         <v>855</v>
       </c>
@@ -16191,8 +16562,11 @@
       <c r="R125" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S125" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
         <v>859</v>
       </c>
@@ -16247,8 +16621,11 @@
       <c r="R126" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S126" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127" s="1" t="s">
         <v>863</v>
       </c>
@@ -16303,8 +16680,11 @@
       <c r="R127" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S127" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128" s="1" t="s">
         <v>869</v>
       </c>
@@ -16359,8 +16739,11 @@
       <c r="R128" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S128" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
         <v>876</v>
       </c>
@@ -16415,8 +16798,11 @@
       <c r="R129" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S129" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
         <v>879</v>
       </c>
@@ -16471,8 +16857,11 @@
       <c r="R130" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S130" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131" s="1" t="s">
         <v>882</v>
       </c>
@@ -16527,8 +16916,11 @@
       <c r="R131" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S131" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132" s="1" t="s">
         <v>885</v>
       </c>
@@ -16583,8 +16975,11 @@
       <c r="R132" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S132" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
         <v>891</v>
       </c>
@@ -16639,8 +17034,11 @@
       <c r="R133" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S133" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
         <v>896</v>
       </c>
@@ -16695,8 +17093,11 @@
       <c r="R134" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S134" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
         <v>903</v>
       </c>
@@ -16751,8 +17152,11 @@
       <c r="R135" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S135" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
         <v>909</v>
       </c>
@@ -16807,8 +17211,11 @@
       <c r="R136" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S136" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
         <v>915</v>
       </c>
@@ -16863,8 +17270,11 @@
       <c r="R137" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S137" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138" s="1" t="s">
         <v>920</v>
       </c>
@@ -16919,8 +17329,11 @@
       <c r="R138" s="1" t="s">
         <v>2704</v>
       </c>
-    </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S138" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139" s="1" t="s">
         <v>927</v>
       </c>
@@ -16975,8 +17388,11 @@
       <c r="R139" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S139" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140" s="1" t="s">
         <v>932</v>
       </c>
@@ -17031,8 +17447,11 @@
       <c r="R140" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S140" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141" s="1" t="s">
         <v>938</v>
       </c>
@@ -17087,8 +17506,11 @@
       <c r="R141" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S141" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142" s="1" t="s">
         <v>944</v>
       </c>
@@ -17143,8 +17565,11 @@
       <c r="R142" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S142" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143" s="1" t="s">
         <v>950</v>
       </c>
@@ -17199,8 +17624,11 @@
       <c r="R143" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S143" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144" s="1" t="s">
         <v>956</v>
       </c>
@@ -17255,8 +17683,11 @@
       <c r="R144" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S144" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145" s="1" t="s">
         <v>962</v>
       </c>
@@ -17311,8 +17742,11 @@
       <c r="R145" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S145" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146" s="1" t="s">
         <v>969</v>
       </c>
@@ -17367,8 +17801,11 @@
       <c r="R146" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S146" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147" s="1" t="s">
         <v>975</v>
       </c>
@@ -17423,8 +17860,11 @@
       <c r="R147" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S147" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148" s="1" t="s">
         <v>981</v>
       </c>
@@ -17479,8 +17919,11 @@
       <c r="R148" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S148" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149" s="1" t="s">
         <v>986</v>
       </c>
@@ -17535,8 +17978,11 @@
       <c r="R149" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S149" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150" s="1" t="s">
         <v>988</v>
       </c>
@@ -17591,8 +18037,11 @@
       <c r="R150" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S150" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151" s="1" t="s">
         <v>994</v>
       </c>
@@ -17647,8 +18096,11 @@
       <c r="R151" s="1" t="s">
         <v>2703</v>
       </c>
-    </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S151" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152" s="1" t="s">
         <v>1000</v>
       </c>
@@ -17703,8 +18155,11 @@
       <c r="R152" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S152" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153" s="1" t="s">
         <v>1006</v>
       </c>
@@ -17759,8 +18214,11 @@
       <c r="R153" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S153" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154" s="1" t="s">
         <v>1013</v>
       </c>
@@ -17815,8 +18273,11 @@
       <c r="R154" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S154" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155" s="1" t="s">
         <v>1018</v>
       </c>
@@ -17871,8 +18332,11 @@
       <c r="R155" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S155" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156" s="1" t="s">
         <v>1023</v>
       </c>
@@ -17927,8 +18391,11 @@
       <c r="R156" s="1" t="s">
         <v>2702</v>
       </c>
-    </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S156" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157" s="1" t="s">
         <v>1030</v>
       </c>
@@ -17983,8 +18450,11 @@
       <c r="R157" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S157" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="158" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A158" s="1" t="s">
         <v>1035</v>
       </c>
@@ -18039,8 +18509,11 @@
       <c r="R158" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S158" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="159" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A159" s="1" t="s">
         <v>1041</v>
       </c>
@@ -18095,8 +18568,11 @@
       <c r="R159" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S159" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="160" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A160" s="1" t="s">
         <v>1046</v>
       </c>
@@ -18151,8 +18627,11 @@
       <c r="R160" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S160" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="161" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A161" s="1" t="s">
         <v>1050</v>
       </c>
@@ -18207,8 +18686,11 @@
       <c r="R161" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S161" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="162" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A162" s="1" t="s">
         <v>1056</v>
       </c>
@@ -18263,8 +18745,11 @@
       <c r="R162" s="1" t="s">
         <v>2701</v>
       </c>
-    </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S162" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A163" s="1" t="s">
         <v>1062</v>
       </c>
@@ -18319,8 +18804,11 @@
       <c r="R163" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S163" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A164" s="1" t="s">
         <v>1068</v>
       </c>
@@ -18375,8 +18863,11 @@
       <c r="R164" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S164" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A165" s="1" t="s">
         <v>1075</v>
       </c>
@@ -18431,8 +18922,11 @@
       <c r="R165" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S165" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A166" s="1" t="s">
         <v>1081</v>
       </c>
@@ -18487,8 +18981,11 @@
       <c r="R166" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S166" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A167" s="1" t="s">
         <v>1087</v>
       </c>
@@ -18543,8 +19040,11 @@
       <c r="R167" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S167" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A168" s="1" t="s">
         <v>1092</v>
       </c>
@@ -18599,8 +19099,11 @@
       <c r="R168" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S168" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A169" s="1" t="s">
         <v>1097</v>
       </c>
@@ -18655,8 +19158,11 @@
       <c r="R169" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S169" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A170" s="1" t="s">
         <v>1102</v>
       </c>
@@ -18711,8 +19217,11 @@
       <c r="R170" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S170" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A171" s="1" t="s">
         <v>1107</v>
       </c>
@@ -18767,8 +19276,11 @@
       <c r="R171" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S171" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A172" s="1" t="s">
         <v>1114</v>
       </c>
@@ -18823,8 +19335,11 @@
       <c r="R172" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S172" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A173" s="1" t="s">
         <v>1120</v>
       </c>
@@ -18879,8 +19394,11 @@
       <c r="R173" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S173" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A174" s="1" t="s">
         <v>1126</v>
       </c>
@@ -18935,8 +19453,11 @@
       <c r="R174" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S174" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A175" s="1" t="s">
         <v>1130</v>
       </c>
@@ -18991,8 +19512,11 @@
       <c r="R175" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S175" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A176" s="1" t="s">
         <v>1136</v>
       </c>
@@ -19047,8 +19571,11 @@
       <c r="R176" s="1" t="s">
         <v>2705</v>
       </c>
-    </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S176" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="177" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A177" s="1" t="s">
         <v>1141</v>
       </c>
@@ -19103,8 +19630,11 @@
       <c r="R177" s="1" t="s">
         <v>2708</v>
       </c>
-    </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S177" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="178" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A178" s="1" t="s">
         <v>1146</v>
       </c>
@@ -19159,8 +19689,11 @@
       <c r="R178" s="1" t="s">
         <v>2709</v>
       </c>
-    </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S178" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="179" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A179" s="1" t="s">
         <v>1152</v>
       </c>
@@ -19215,8 +19748,11 @@
       <c r="R179" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S179" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="180" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A180" s="1" t="s">
         <v>1157</v>
       </c>
@@ -19271,8 +19807,11 @@
       <c r="R180" s="1" t="s">
         <v>2713</v>
       </c>
-    </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S180" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="181" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A181" s="1" t="s">
         <v>1162</v>
       </c>
@@ -19327,8 +19866,11 @@
       <c r="R181" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S181" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="182" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A182" s="1" t="s">
         <v>1168</v>
       </c>
@@ -19383,8 +19925,11 @@
       <c r="R182" s="1" t="s">
         <v>2716</v>
       </c>
-    </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S182" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="183" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A183" s="1" t="s">
         <v>1174</v>
       </c>
@@ -19439,8 +19984,11 @@
       <c r="R183" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S183" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="184" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A184" s="1" t="s">
         <v>1180</v>
       </c>
@@ -19495,8 +20043,11 @@
       <c r="R184" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S184" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="185" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A185" s="1" t="s">
         <v>1185</v>
       </c>
@@ -19551,8 +20102,11 @@
       <c r="R185" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S185" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="186" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A186" s="1" t="s">
         <v>1190</v>
       </c>
@@ -19607,8 +20161,11 @@
       <c r="R186" t="s">
         <v>2717</v>
       </c>
-    </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S186" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="187" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A187" s="1" t="s">
         <v>1196</v>
       </c>
@@ -19663,8 +20220,11 @@
       <c r="R187" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S187" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="188" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A188" s="1" t="s">
         <v>1202</v>
       </c>
@@ -19719,8 +20279,11 @@
       <c r="R188" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S188" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="189" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A189" s="1" t="s">
         <v>1207</v>
       </c>
@@ -19775,8 +20338,11 @@
       <c r="R189" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S189" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="190" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A190" s="1" t="s">
         <v>1213</v>
       </c>
@@ -19831,8 +20397,11 @@
       <c r="R190" s="1" t="s">
         <v>2719</v>
       </c>
-    </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S190" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="191" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A191" s="1" t="s">
         <v>1219</v>
       </c>
@@ -19887,8 +20456,11 @@
       <c r="R191" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S191" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="192" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A192" s="1" t="s">
         <v>1224</v>
       </c>
@@ -19934,8 +20506,11 @@
       <c r="O192" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S192" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="193" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A193" s="1" t="s">
         <v>1231</v>
       </c>
@@ -19990,8 +20565,11 @@
       <c r="R193" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S193" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A194" s="1" t="s">
         <v>1237</v>
       </c>
@@ -20046,8 +20624,11 @@
       <c r="R194" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S194" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A195" s="1" t="s">
         <v>1241</v>
       </c>
@@ -20102,8 +20683,11 @@
       <c r="R195" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S195" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A196" s="1" t="s">
         <v>1246</v>
       </c>
@@ -20158,8 +20742,11 @@
       <c r="R196" s="1" t="s">
         <v>2723</v>
       </c>
-    </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S196" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A197" s="1" t="s">
         <v>1252</v>
       </c>
@@ -20214,8 +20801,11 @@
       <c r="R197" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S197" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A198" s="1" t="s">
         <v>1257</v>
       </c>
@@ -20270,8 +20860,11 @@
       <c r="R198" s="1" t="s">
         <v>2725</v>
       </c>
-    </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S198" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A199" s="1" t="s">
         <v>1263</v>
       </c>
@@ -20326,8 +20919,11 @@
       <c r="R199" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S199" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A200" s="1" t="s">
         <v>1270</v>
       </c>
@@ -20382,8 +20978,11 @@
       <c r="R200" s="1" t="s">
         <v>2744</v>
       </c>
-    </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S200" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A201" s="1" t="s">
         <v>1276</v>
       </c>
@@ -20438,8 +21037,11 @@
       <c r="R201" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S201" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="202" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A202" s="1" t="s">
         <v>1282</v>
       </c>
@@ -20494,8 +21096,11 @@
       <c r="R202" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S202" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="203" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A203" s="1" t="s">
         <v>1287</v>
       </c>
@@ -20550,8 +21155,11 @@
       <c r="R203" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S203" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="204" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A204" s="1" t="s">
         <v>1292</v>
       </c>
@@ -20606,8 +21214,11 @@
       <c r="R204" s="1" t="s">
         <v>2740</v>
       </c>
-    </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S204" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="205" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A205" s="1" t="s">
         <v>1299</v>
       </c>
@@ -20662,8 +21273,11 @@
       <c r="R205" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S205" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="206" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A206" s="1" t="s">
         <v>1303</v>
       </c>
@@ -20718,8 +21332,11 @@
       <c r="R206" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S206" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="207" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A207" s="1" t="s">
         <v>1309</v>
       </c>
@@ -20774,8 +21391,11 @@
       <c r="R207" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S207" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="208" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A208" s="1" t="s">
         <v>1312</v>
       </c>
@@ -20830,8 +21450,11 @@
       <c r="R208" s="1" t="s">
         <v>2739</v>
       </c>
-    </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S208" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="209" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A209" s="1" t="s">
         <v>1318</v>
       </c>
@@ -20886,8 +21509,11 @@
       <c r="R209" s="1" t="s">
         <v>2734</v>
       </c>
-    </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S209" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="210" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>1324</v>
       </c>
@@ -20942,8 +21568,11 @@
       <c r="R210" s="1" t="s">
         <v>2730</v>
       </c>
-    </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S210" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="211" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A211" s="1" t="s">
         <v>1329</v>
       </c>
@@ -20998,8 +21627,11 @@
       <c r="R211" s="1" t="s">
         <v>2733</v>
       </c>
-    </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S211" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="212" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A212" s="1" t="s">
         <v>1334</v>
       </c>
@@ -21054,8 +21686,11 @@
       <c r="R212" s="1" t="s">
         <v>2726</v>
       </c>
-    </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S212" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="213" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A213" s="1" t="s">
         <v>1339</v>
       </c>
@@ -21110,8 +21745,11 @@
       <c r="R213" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S213" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="214" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A214" s="1" t="s">
         <v>1344</v>
       </c>
@@ -21166,8 +21804,11 @@
       <c r="R214" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S214" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="215" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A215" s="1" t="s">
         <v>1350</v>
       </c>
@@ -21222,8 +21863,11 @@
       <c r="R215" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S215" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="216" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A216" s="1" t="s">
         <v>1355</v>
       </c>
@@ -21278,8 +21922,11 @@
       <c r="R216" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S216" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="217" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>1358</v>
       </c>
@@ -21334,8 +21981,11 @@
       <c r="R217" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S217" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="218" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A218" s="1" t="s">
         <v>1363</v>
       </c>
@@ -21390,8 +22040,11 @@
       <c r="R218" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S218" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="219" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A219" s="1" t="s">
         <v>1369</v>
       </c>
@@ -21446,8 +22099,11 @@
       <c r="R219" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S219" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="220" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A220" s="1" t="s">
         <v>1374</v>
       </c>
@@ -21502,8 +22158,11 @@
       <c r="R220" s="1" t="s">
         <v>2743</v>
       </c>
-    </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S220" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="221" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A221" s="1" t="s">
         <v>1380</v>
       </c>
@@ -21558,8 +22217,11 @@
       <c r="R221" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S221" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="222" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A222" s="1" t="s">
         <v>1385</v>
       </c>
@@ -21614,8 +22276,11 @@
       <c r="R222" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S222" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="223" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A223" s="1" t="s">
         <v>1390</v>
       </c>
@@ -21670,8 +22335,11 @@
       <c r="R223" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S223" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="224" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A224" s="1" t="s">
         <v>1395</v>
       </c>
@@ -21726,8 +22394,11 @@
       <c r="R224" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S224" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="225" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A225" s="1" t="s">
         <v>1401</v>
       </c>
@@ -21782,8 +22453,11 @@
       <c r="R225" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S225" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="226" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A226" s="1" t="s">
         <v>1405</v>
       </c>
@@ -21838,8 +22512,11 @@
       <c r="R226" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S226" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="227" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A227" s="1" t="s">
         <v>1409</v>
       </c>
@@ -21894,8 +22571,11 @@
       <c r="R227" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S227" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="228" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A228" s="1" t="s">
         <v>1415</v>
       </c>
@@ -21950,8 +22630,11 @@
       <c r="R228" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S228" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="229" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A229" s="1" t="s">
         <v>1421</v>
       </c>
@@ -22006,8 +22689,11 @@
       <c r="R229" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S229" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="230" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A230" s="1" t="s">
         <v>1427</v>
       </c>
@@ -22062,8 +22748,11 @@
       <c r="R230" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S230" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="231" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A231" s="1" t="s">
         <v>1433</v>
       </c>
@@ -22118,8 +22807,11 @@
       <c r="R231" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S231" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="232" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A232" s="1" t="s">
         <v>1438</v>
       </c>
@@ -22174,8 +22866,11 @@
       <c r="R232" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S232" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="233" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A233" s="1" t="s">
         <v>1443</v>
       </c>
@@ -22230,8 +22925,11 @@
       <c r="R233" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S233" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="234" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A234" s="1" t="s">
         <v>1448</v>
       </c>
@@ -22286,8 +22984,11 @@
       <c r="R234" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S234" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="235" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A235" s="1" t="s">
         <v>1453</v>
       </c>
@@ -22342,8 +23043,11 @@
       <c r="R235" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S235" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="236" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A236" s="1" t="s">
         <v>1459</v>
       </c>
@@ -22398,8 +23102,11 @@
       <c r="R236" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S236" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="237" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A237" s="1" t="s">
         <v>1464</v>
       </c>
@@ -22454,8 +23161,11 @@
       <c r="R237" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S237" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="238" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A238" s="1" t="s">
         <v>1469</v>
       </c>
@@ -22510,8 +23220,11 @@
       <c r="R238" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S238" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="239" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A239" s="1" t="s">
         <v>1474</v>
       </c>
@@ -22566,8 +23279,11 @@
       <c r="R239" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S239" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="240" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>1479</v>
       </c>
@@ -22622,8 +23338,11 @@
       <c r="R240" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S240" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="241" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A241" s="1" t="s">
         <v>1484</v>
       </c>
@@ -22678,8 +23397,11 @@
       <c r="R241" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S241" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="242" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A242" s="1" t="s">
         <v>1489</v>
       </c>
@@ -22734,8 +23456,11 @@
       <c r="R242" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S242" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="243" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A243" s="1" t="s">
         <v>1494</v>
       </c>
@@ -22790,8 +23515,11 @@
       <c r="R243" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S243" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="244" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A244" s="1" t="s">
         <v>1499</v>
       </c>
@@ -22846,8 +23574,11 @@
       <c r="R244" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S244" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="245" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A245" s="1" t="s">
         <v>1503</v>
       </c>
@@ -22902,8 +23633,11 @@
       <c r="R245" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S245" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="246" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A246" s="1" t="s">
         <v>1506</v>
       </c>
@@ -22958,8 +23692,11 @@
       <c r="R246" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S246" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="247" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A247" s="1" t="s">
         <v>1511</v>
       </c>
@@ -23014,8 +23751,11 @@
       <c r="R247" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S247" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="248" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A248" s="1" t="s">
         <v>1515</v>
       </c>
@@ -23070,8 +23810,11 @@
       <c r="R248" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S248" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="249" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A249" s="1" t="s">
         <v>1518</v>
       </c>
@@ -23126,8 +23869,11 @@
       <c r="R249" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S249" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="250" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A250" s="1" t="s">
         <v>1522</v>
       </c>
@@ -23182,8 +23928,11 @@
       <c r="R250" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S250" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="251" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A251" s="1" t="s">
         <v>1528</v>
       </c>
@@ -23238,8 +23987,11 @@
       <c r="R251" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S251" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="252" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A252" s="1" t="s">
         <v>1533</v>
       </c>
@@ -23294,8 +24046,11 @@
       <c r="R252" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S252" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="253" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A253" s="1" t="s">
         <v>1538</v>
       </c>
@@ -23350,8 +24105,11 @@
       <c r="R253" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S253" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="254" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A254" s="1" t="s">
         <v>1543</v>
       </c>
@@ -23406,8 +24164,11 @@
       <c r="R254" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S254" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="255" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A255" s="1" t="s">
         <v>1547</v>
       </c>
@@ -23462,8 +24223,11 @@
       <c r="R255" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S255" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="256" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A256" s="1" t="s">
         <v>1551</v>
       </c>
@@ -23518,8 +24282,11 @@
       <c r="R256" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S256" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="257" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A257" s="1" t="s">
         <v>1555</v>
       </c>
@@ -23574,8 +24341,11 @@
       <c r="R257" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S257" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="258" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A258" s="1" t="s">
         <v>1560</v>
       </c>
@@ -23630,8 +24400,11 @@
       <c r="R258" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S258" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="259" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A259" s="1" t="s">
         <v>1566</v>
       </c>
@@ -23686,8 +24459,11 @@
       <c r="R259" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S259" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="260" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A260" s="1" t="s">
         <v>1571</v>
       </c>
@@ -23742,8 +24518,11 @@
       <c r="R260" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S260" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="261" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A261" s="1" t="s">
         <v>1575</v>
       </c>
@@ -23798,8 +24577,11 @@
       <c r="R261" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S261" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="262" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A262" s="1" t="s">
         <v>1580</v>
       </c>
@@ -23854,8 +24636,11 @@
       <c r="R262" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S262" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="263" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A263" s="1" t="s">
         <v>1585</v>
       </c>
@@ -23910,8 +24695,11 @@
       <c r="R263" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S263" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="264" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A264" s="1" t="s">
         <v>1590</v>
       </c>
@@ -23966,8 +24754,11 @@
       <c r="R264" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S264" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="265" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A265" s="1" t="s">
         <v>1596</v>
       </c>
@@ -24022,8 +24813,11 @@
       <c r="R265" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S265" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="266" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A266" s="1" t="s">
         <v>1600</v>
       </c>
@@ -24078,8 +24872,11 @@
       <c r="R266" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S266" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="267" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A267" s="1" t="s">
         <v>1603</v>
       </c>
@@ -24134,8 +24931,11 @@
       <c r="R267" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S267" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="268" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A268" s="1" t="s">
         <v>1607</v>
       </c>
@@ -24190,8 +24990,11 @@
       <c r="R268" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S268" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="269" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>1613</v>
       </c>
@@ -24246,8 +25049,11 @@
       <c r="R269" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S269" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="270" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A270" s="1" t="s">
         <v>1619</v>
       </c>
@@ -24302,8 +25108,11 @@
       <c r="R270" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S270" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="271" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A271" s="1" t="s">
         <v>1626</v>
       </c>
@@ -24358,8 +25167,11 @@
       <c r="R271" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S271" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="272" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A272" s="1" t="s">
         <v>1632</v>
       </c>
@@ -24414,8 +25226,11 @@
       <c r="R272" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S272" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="273" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A273" s="1" t="s">
         <v>1638</v>
       </c>
@@ -24470,8 +25285,11 @@
       <c r="R273" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S273" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="274" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A274" s="1" t="s">
         <v>1643</v>
       </c>
@@ -24526,8 +25344,11 @@
       <c r="R274" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S274" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="275" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A275" s="1" t="s">
         <v>1649</v>
       </c>
@@ -24582,8 +25403,11 @@
       <c r="R275" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S275" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="276" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>1654</v>
       </c>
@@ -24638,8 +25462,11 @@
       <c r="R276" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S276" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="277" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>1660</v>
       </c>
@@ -24694,8 +25521,11 @@
       <c r="R277" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S277" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="278" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A278" s="1" t="s">
         <v>1666</v>
       </c>
@@ -24750,8 +25580,11 @@
       <c r="R278" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S278" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="279" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A279" s="1" t="s">
         <v>1671</v>
       </c>
@@ -24806,8 +25639,11 @@
       <c r="R279" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S279" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="280" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A280" s="1" t="s">
         <v>1677</v>
       </c>
@@ -24862,8 +25698,11 @@
       <c r="R280" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S280" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="281" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A281" s="1" t="s">
         <v>1682</v>
       </c>
@@ -24918,8 +25757,11 @@
       <c r="R281" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S281" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="282" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A282" s="1" t="s">
         <v>1686</v>
       </c>
@@ -24974,8 +25816,11 @@
       <c r="R282" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S282" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="283" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A283" s="1" t="s">
         <v>1691</v>
       </c>
@@ -25030,8 +25875,11 @@
       <c r="R283" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S283" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="284" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A284" s="1" t="s">
         <v>1696</v>
       </c>
@@ -25086,8 +25934,11 @@
       <c r="R284" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S284" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="285" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A285" s="1" t="s">
         <v>1701</v>
       </c>
@@ -25142,8 +25993,11 @@
       <c r="R285" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S285" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="286" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A286" s="1" t="s">
         <v>1706</v>
       </c>
@@ -25198,8 +26052,11 @@
       <c r="R286" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S286" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="287" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A287" s="1" t="s">
         <v>1710</v>
       </c>
@@ -25254,8 +26111,11 @@
       <c r="R287" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S287" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="288" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A288" s="1" t="s">
         <v>1715</v>
       </c>
@@ -25310,8 +26170,11 @@
       <c r="R288" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S288" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="289" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A289" s="1" t="s">
         <v>1718</v>
       </c>
@@ -25366,8 +26229,11 @@
       <c r="R289" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S289" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="290" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A290" s="1" t="s">
         <v>1722</v>
       </c>
@@ -25422,8 +26288,11 @@
       <c r="R290" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S290" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="291" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>1726</v>
       </c>
@@ -25478,8 +26347,11 @@
       <c r="R291" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S291" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="292" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A292" s="1" t="s">
         <v>1732</v>
       </c>
@@ -25534,8 +26406,11 @@
       <c r="R292" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S292" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="293" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A293" s="1" t="s">
         <v>1736</v>
       </c>
@@ -25590,8 +26465,11 @@
       <c r="R293" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S293" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="294" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A294" s="1" t="s">
         <v>1741</v>
       </c>
@@ -25646,8 +26524,11 @@
       <c r="R294" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S294" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="295" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A295" s="1" t="s">
         <v>1744</v>
       </c>
@@ -25702,8 +26583,11 @@
       <c r="R295" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S295" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="296" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A296" s="1" t="s">
         <v>1748</v>
       </c>
@@ -25758,8 +26642,11 @@
       <c r="R296" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S296" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="297" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A297" s="1" t="s">
         <v>1752</v>
       </c>
@@ -25814,8 +26701,11 @@
       <c r="R297" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S297" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="298" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A298" s="1" t="s">
         <v>1757</v>
       </c>
@@ -25870,8 +26760,11 @@
       <c r="R298" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S298" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="299" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A299" s="1" t="s">
         <v>1762</v>
       </c>
@@ -25926,8 +26819,11 @@
       <c r="R299" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S299" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="300" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A300" s="1" t="s">
         <v>1766</v>
       </c>
@@ -25982,8 +26878,11 @@
       <c r="R300" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S300" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="301" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A301" s="1" t="s">
         <v>1769</v>
       </c>
@@ -26038,8 +26937,11 @@
       <c r="R301" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S301" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="302" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A302" s="1" t="s">
         <v>1773</v>
       </c>
@@ -26094,8 +26996,11 @@
       <c r="R302" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S302" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="303" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A303" s="1" t="s">
         <v>1777</v>
       </c>
@@ -26150,8 +27055,11 @@
       <c r="R303" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S303" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="304" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A304" s="1" t="s">
         <v>1783</v>
       </c>
@@ -26206,8 +27114,11 @@
       <c r="R304" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S304" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="305" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A305" s="1" t="s">
         <v>1787</v>
       </c>
@@ -26262,8 +27173,11 @@
       <c r="R305" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S305" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="306" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A306" s="1" t="s">
         <v>1792</v>
       </c>
@@ -26318,8 +27232,11 @@
       <c r="R306" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S306" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="307" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A307" s="1" t="s">
         <v>1797</v>
       </c>
@@ -26374,8 +27291,11 @@
       <c r="R307" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S307" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="308" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A308" s="1" t="s">
         <v>1802</v>
       </c>
@@ -26430,8 +27350,11 @@
       <c r="R308" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S308" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="309" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A309" s="1" t="s">
         <v>1806</v>
       </c>
@@ -26486,8 +27409,11 @@
       <c r="R309" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S309" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="310" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A310" s="1" t="s">
         <v>1811</v>
       </c>
@@ -26542,8 +27468,11 @@
       <c r="R310" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S310" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="311" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A311" s="1" t="s">
         <v>1816</v>
       </c>
@@ -26598,8 +27527,11 @@
       <c r="R311" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S311" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="312" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A312" s="1" t="s">
         <v>1821</v>
       </c>
@@ -26654,8 +27586,11 @@
       <c r="R312" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S312" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="313" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A313" s="1" t="s">
         <v>1826</v>
       </c>
@@ -26710,8 +27645,11 @@
       <c r="R313" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S313" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="314" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A314" s="1" t="s">
         <v>1831</v>
       </c>
@@ -26766,8 +27704,11 @@
       <c r="R314" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S314" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="315" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A315" s="1" t="s">
         <v>1836</v>
       </c>
@@ -26822,8 +27763,11 @@
       <c r="R315" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S315" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="316" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A316" s="1" t="s">
         <v>1840</v>
       </c>
@@ -26878,8 +27822,11 @@
       <c r="R316" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S316" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="317" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A317" s="1" t="s">
         <v>1843</v>
       </c>
@@ -26934,8 +27881,11 @@
       <c r="R317" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S317" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="318" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A318" s="1" t="s">
         <v>1846</v>
       </c>
@@ -26990,8 +27940,11 @@
       <c r="R318" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S318" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="319" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A319" s="1" t="s">
         <v>1850</v>
       </c>
@@ -27046,8 +27999,11 @@
       <c r="R319" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S319" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="320" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A320" s="1" t="s">
         <v>1853</v>
       </c>
@@ -27102,8 +28058,11 @@
       <c r="R320" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S320" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="321" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A321" s="1" t="s">
         <v>1856</v>
       </c>
@@ -27158,8 +28117,11 @@
       <c r="R321" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S321" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="322" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A322" s="1" t="s">
         <v>1860</v>
       </c>
@@ -27214,8 +28176,11 @@
       <c r="R322" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S322" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="323" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A323" s="1" t="s">
         <v>1864</v>
       </c>
@@ -27270,8 +28235,11 @@
       <c r="R323" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S323" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="324" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A324" s="1" t="s">
         <v>1868</v>
       </c>
@@ -27326,8 +28294,11 @@
       <c r="R324" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S324" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="325" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A325" s="1" t="s">
         <v>1872</v>
       </c>
@@ -27382,8 +28353,11 @@
       <c r="R325" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S325" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="326" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A326" s="1" t="s">
         <v>1876</v>
       </c>
@@ -27438,8 +28412,11 @@
       <c r="R326" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S326" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="327" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A327" s="1" t="s">
         <v>1880</v>
       </c>
@@ -27494,8 +28471,11 @@
       <c r="R327" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S327" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="328" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A328" s="1" t="s">
         <v>1884</v>
       </c>
@@ -27550,8 +28530,11 @@
       <c r="R328" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S328" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="329" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A329" s="1" t="s">
         <v>1888</v>
       </c>
@@ -27606,8 +28589,11 @@
       <c r="R329" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S329" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="330" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A330" s="1" t="s">
         <v>1892</v>
       </c>
@@ -27662,8 +28648,11 @@
       <c r="R330" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S330" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="331" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A331" s="1" t="s">
         <v>1896</v>
       </c>
@@ -27718,8 +28707,11 @@
       <c r="R331" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S331" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="332" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A332" s="1" t="s">
         <v>1900</v>
       </c>
@@ -27774,8 +28766,11 @@
       <c r="R332" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S332" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="333" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A333" s="1" t="s">
         <v>1904</v>
       </c>
@@ -27830,8 +28825,11 @@
       <c r="R333" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S333" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="334" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A334" s="1" t="s">
         <v>1908</v>
       </c>
@@ -27886,8 +28884,11 @@
       <c r="R334" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S334" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="335" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A335" s="1" t="s">
         <v>1911</v>
       </c>
@@ -27942,8 +28943,11 @@
       <c r="R335" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S335" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="336" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A336" s="1" t="s">
         <v>1915</v>
       </c>
@@ -27998,8 +29002,11 @@
       <c r="R336" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S336" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="337" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A337" s="1" t="s">
         <v>1919</v>
       </c>
@@ -28054,8 +29061,11 @@
       <c r="R337" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S337" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="338" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A338" s="1" t="s">
         <v>1923</v>
       </c>
@@ -28110,8 +29120,11 @@
       <c r="R338" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S338" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="339" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A339" s="1" t="s">
         <v>1926</v>
       </c>
@@ -28166,8 +29179,11 @@
       <c r="R339" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S339" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="340" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A340" s="1" t="s">
         <v>1929</v>
       </c>
@@ -28222,8 +29238,11 @@
       <c r="R340" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S340" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="341" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A341" s="1" t="s">
         <v>1932</v>
       </c>
@@ -28278,8 +29297,11 @@
       <c r="R341" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S341" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="342" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A342" s="1" t="s">
         <v>1935</v>
       </c>
@@ -28334,8 +29356,11 @@
       <c r="R342" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S342" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="343" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A343" s="1" t="s">
         <v>1938</v>
       </c>
@@ -28390,8 +29415,11 @@
       <c r="R343" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S343" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="344" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A344" s="1" t="s">
         <v>1941</v>
       </c>
@@ -28446,8 +29474,11 @@
       <c r="R344" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S344" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="345" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A345" s="1" t="s">
         <v>1944</v>
       </c>
@@ -28502,8 +29533,11 @@
       <c r="R345" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S345" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="346" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A346" s="1" t="s">
         <v>1947</v>
       </c>
@@ -28558,8 +29592,11 @@
       <c r="R346" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S346" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A347" s="1" t="s">
         <v>1950</v>
       </c>
@@ -28614,8 +29651,11 @@
       <c r="R347" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S347" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A348" s="1" t="s">
         <v>1953</v>
       </c>
@@ -28670,8 +29710,11 @@
       <c r="R348" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S348" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="349" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A349" s="1" t="s">
         <v>1956</v>
       </c>
@@ -28726,8 +29769,11 @@
       <c r="R349" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S349" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="350" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A350" s="1" t="s">
         <v>1960</v>
       </c>
@@ -28782,8 +29828,11 @@
       <c r="R350" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S350" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="351" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A351" s="1" t="s">
         <v>1964</v>
       </c>
@@ -28838,8 +29887,11 @@
       <c r="R351" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S351" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="352" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A352" s="1" t="s">
         <v>1968</v>
       </c>
@@ -28894,8 +29946,11 @@
       <c r="R352" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S352" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="353" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A353" s="1" t="s">
         <v>1972</v>
       </c>
@@ -28950,8 +30005,11 @@
       <c r="R353" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S353" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="354" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A354" s="1" t="s">
         <v>1976</v>
       </c>
@@ -29006,8 +30064,11 @@
       <c r="R354" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S354" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="355" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>1980</v>
       </c>
@@ -29062,8 +30123,11 @@
       <c r="R355" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S355" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="356" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A356" s="1" t="s">
         <v>1984</v>
       </c>
@@ -29118,8 +30182,11 @@
       <c r="R356" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S356" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="357" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A357" s="1" t="s">
         <v>1988</v>
       </c>
@@ -29174,8 +30241,11 @@
       <c r="R357" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S357" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="358" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A358" s="1" t="s">
         <v>1992</v>
       </c>
@@ -29230,8 +30300,11 @@
       <c r="R358" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S358" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="359" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A359" s="1" t="s">
         <v>1996</v>
       </c>
@@ -29286,8 +30359,11 @@
       <c r="R359" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S359" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="360" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>1999</v>
       </c>
@@ -29342,8 +30418,11 @@
       <c r="R360" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S360" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="361" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A361" s="1" t="s">
         <v>2002</v>
       </c>
@@ -29398,8 +30477,11 @@
       <c r="R361" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S361" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="362" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A362" s="1" t="s">
         <v>2005</v>
       </c>
@@ -29454,8 +30536,11 @@
       <c r="R362" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S362" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="363" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A363" s="1" t="s">
         <v>2008</v>
       </c>
@@ -29510,8 +30595,11 @@
       <c r="R363" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S363" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="364" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A364" s="1" t="s">
         <v>2012</v>
       </c>
@@ -29566,8 +30654,11 @@
       <c r="R364" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S364" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="365" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A365" s="1" t="s">
         <v>2016</v>
       </c>
@@ -29622,8 +30713,11 @@
       <c r="R365" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="366" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S365" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="366" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A366" s="1" t="s">
         <v>2020</v>
       </c>
@@ -29678,8 +30772,11 @@
       <c r="R366" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="367" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S366" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="367" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A367" s="1" t="s">
         <v>2024</v>
       </c>
@@ -29734,8 +30831,11 @@
       <c r="R367" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="368" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S367" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="368" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A368" s="1" t="s">
         <v>2028</v>
       </c>
@@ -29790,8 +30890,11 @@
       <c r="R368" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S368" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="369" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A369" s="1" t="s">
         <v>2032</v>
       </c>
@@ -29846,8 +30949,11 @@
       <c r="R369" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S369" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="370" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A370" s="1" t="s">
         <v>2036</v>
       </c>
@@ -29902,8 +31008,11 @@
       <c r="R370" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S370" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="371" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A371" s="1" t="s">
         <v>2040</v>
       </c>
@@ -29958,8 +31067,11 @@
       <c r="R371" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S371" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="372" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A372" s="1" t="s">
         <v>2044</v>
       </c>
@@ -30014,8 +31126,11 @@
       <c r="R372" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S372" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="373" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A373" s="1" t="s">
         <v>2048</v>
       </c>
@@ -30070,8 +31185,11 @@
       <c r="R373" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S373" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="374" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A374" s="1" t="s">
         <v>2052</v>
       </c>
@@ -30126,8 +31244,11 @@
       <c r="R374" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S374" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="375" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A375" s="1" t="s">
         <v>2055</v>
       </c>
@@ -30182,8 +31303,11 @@
       <c r="R375" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S375" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="376" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A376" s="1" t="s">
         <v>2059</v>
       </c>
@@ -30238,8 +31362,11 @@
       <c r="R376" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S376" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="377" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A377" s="1" t="s">
         <v>2063</v>
       </c>
@@ -30294,8 +31421,11 @@
       <c r="R377" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S377" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="378" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A378" s="1" t="s">
         <v>2066</v>
       </c>
@@ -30350,8 +31480,11 @@
       <c r="R378" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S378" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="379" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A379" s="1" t="s">
         <v>2070</v>
       </c>
@@ -30406,8 +31539,11 @@
       <c r="R379" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S379" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="380" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A380" s="1" t="s">
         <v>2075</v>
       </c>
@@ -30462,8 +31598,11 @@
       <c r="R380" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="381" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S380" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="381" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A381" s="1" t="s">
         <v>2079</v>
       </c>
@@ -30518,8 +31657,11 @@
       <c r="R381" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="382" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S381" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="382" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A382" s="1" t="s">
         <v>2083</v>
       </c>
@@ -30574,8 +31716,11 @@
       <c r="R382" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S382" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="383" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A383" s="1" t="s">
         <v>2088</v>
       </c>
@@ -30630,8 +31775,11 @@
       <c r="R383" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S383" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="384" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A384" s="1" t="s">
         <v>2093</v>
       </c>
@@ -30686,8 +31834,11 @@
       <c r="R384" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S384" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="385" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A385" s="1" t="s">
         <v>2098</v>
       </c>
@@ -30742,8 +31893,11 @@
       <c r="R385" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S385" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="386" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A386" s="1" t="s">
         <v>2101</v>
       </c>
@@ -30798,8 +31952,11 @@
       <c r="R386" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S386" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="387" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A387" s="1" t="s">
         <v>2104</v>
       </c>
@@ -30854,8 +32011,11 @@
       <c r="R387" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S387" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="388" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A388" s="1" t="s">
         <v>2107</v>
       </c>
@@ -30910,8 +32070,11 @@
       <c r="R388" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="389" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S388" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="389" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A389" s="1" t="s">
         <v>2111</v>
       </c>
@@ -30966,8 +32129,11 @@
       <c r="R389" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="390" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S389" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="390" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A390" s="1" t="s">
         <v>2115</v>
       </c>
@@ -31022,8 +32188,11 @@
       <c r="R390" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="391" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S390" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="391" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A391" s="1" t="s">
         <v>2119</v>
       </c>
@@ -31078,8 +32247,11 @@
       <c r="R391" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="392" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S391" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="392" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A392" s="1" t="s">
         <v>2123</v>
       </c>
@@ -31134,8 +32306,11 @@
       <c r="R392" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="393" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S392" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="393" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A393" s="1" t="s">
         <v>2127</v>
       </c>
@@ -31190,8 +32365,11 @@
       <c r="R393" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="394" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S393" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A394" s="1" t="s">
         <v>2131</v>
       </c>
@@ -31246,8 +32424,11 @@
       <c r="R394" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="395" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S394" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="395" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A395" s="1" t="s">
         <v>2136</v>
       </c>
@@ -31302,8 +32483,11 @@
       <c r="R395" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="396" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S395" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="396" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A396" s="1" t="s">
         <v>2141</v>
       </c>
@@ -31358,8 +32542,11 @@
       <c r="R396" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="397" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S396" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="397" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A397" s="1" t="s">
         <v>2144</v>
       </c>
@@ -31414,8 +32601,11 @@
       <c r="R397" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="398" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S397" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="398" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A398" s="1" t="s">
         <v>2149</v>
       </c>
@@ -31470,8 +32660,11 @@
       <c r="R398" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="399" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S398" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A399" s="1" t="s">
         <v>2152</v>
       </c>
@@ -31526,8 +32719,11 @@
       <c r="R399" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="400" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S399" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A400" s="1" t="s">
         <v>2155</v>
       </c>
@@ -31582,8 +32778,11 @@
       <c r="R400" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="401" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S400" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="401" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A401" s="1" t="s">
         <v>2159</v>
       </c>
@@ -31638,8 +32837,11 @@
       <c r="R401" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="402" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S401" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="402" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A402" s="1" t="s">
         <v>2163</v>
       </c>
@@ -31694,8 +32896,11 @@
       <c r="R402" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="403" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S402" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="403" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A403" s="1" t="s">
         <v>2167</v>
       </c>
@@ -31750,8 +32955,11 @@
       <c r="R403" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="404" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S403" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="404" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A404" s="1" t="s">
         <v>2171</v>
       </c>
@@ -31806,8 +33014,11 @@
       <c r="R404" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="405" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S404" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="405" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A405" s="1" t="s">
         <v>2176</v>
       </c>
@@ -31862,8 +33073,11 @@
       <c r="R405" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="406" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S405" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="406" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A406" s="1" t="s">
         <v>2179</v>
       </c>
@@ -31918,8 +33132,11 @@
       <c r="R406" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="407" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S406" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="407" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A407" s="1" t="s">
         <v>2181</v>
       </c>
@@ -31974,8 +33191,11 @@
       <c r="R407" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="408" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S407" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="408" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A408" s="1" t="s">
         <v>2186</v>
       </c>
@@ -32030,8 +33250,11 @@
       <c r="R408" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="409" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S408" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="409" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A409" s="1" t="s">
         <v>2192</v>
       </c>
@@ -32086,8 +33309,11 @@
       <c r="R409" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="410" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S409" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="410" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A410" s="1" t="s">
         <v>2196</v>
       </c>
@@ -32142,8 +33368,11 @@
       <c r="R410" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="411" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S410" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="411" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A411" s="1" t="s">
         <v>2198</v>
       </c>
@@ -32198,8 +33427,11 @@
       <c r="R411" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="412" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S411" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="412" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A412" s="1" t="s">
         <v>2202</v>
       </c>
@@ -32254,8 +33486,11 @@
       <c r="R412" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="413" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S412" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="413" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A413" s="1" t="s">
         <v>2208</v>
       </c>
@@ -32310,8 +33545,11 @@
       <c r="R413" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="414" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S413" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="414" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A414" s="1" t="s">
         <v>2213</v>
       </c>
@@ -32366,8 +33604,11 @@
       <c r="R414" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="415" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S414" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="415" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A415" s="1" t="s">
         <v>2218</v>
       </c>
@@ -32422,8 +33663,11 @@
       <c r="R415" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="416" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S415" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="416" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A416" s="1" t="s">
         <v>2223</v>
       </c>
@@ -32478,8 +33722,11 @@
       <c r="R416" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="417" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S416" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="417" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A417" s="1" t="s">
         <v>2226</v>
       </c>
@@ -32534,8 +33781,11 @@
       <c r="R417" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="418" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S417" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="418" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A418" s="1" t="s">
         <v>2230</v>
       </c>
@@ -32590,8 +33840,11 @@
       <c r="R418" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="419" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S418" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="419" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A419" s="1" t="s">
         <v>2235</v>
       </c>
@@ -32646,8 +33899,11 @@
       <c r="R419" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="420" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S419" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="420" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A420" s="1" t="s">
         <v>2241</v>
       </c>
@@ -32702,8 +33958,11 @@
       <c r="R420" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="421" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S420" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="421" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A421" s="1" t="s">
         <v>2244</v>
       </c>
@@ -32758,8 +34017,11 @@
       <c r="R421" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="422" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S421" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="422" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A422" s="1" t="s">
         <v>2249</v>
       </c>
@@ -32814,8 +34076,11 @@
       <c r="R422" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="423" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S422" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="423" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A423" s="1" t="s">
         <v>2254</v>
       </c>
@@ -32870,8 +34135,11 @@
       <c r="R423" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="424" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S423" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="424" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A424" s="1" t="s">
         <v>2258</v>
       </c>
@@ -32926,8 +34194,11 @@
       <c r="R424" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="425" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S424" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="425" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A425" s="1" t="s">
         <v>2262</v>
       </c>
@@ -32982,8 +34253,11 @@
       <c r="R425" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="426" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S425" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="426" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A426" s="1" t="s">
         <v>2267</v>
       </c>
@@ -33038,8 +34312,11 @@
       <c r="R426" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="427" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S426" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="427" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A427" s="1" t="s">
         <v>2272</v>
       </c>
@@ -33094,8 +34371,11 @@
       <c r="R427" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="428" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S427" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="428" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A428" s="1" t="s">
         <v>2276</v>
       </c>
@@ -33150,8 +34430,11 @@
       <c r="R428" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="429" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S428" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="429" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A429" s="1" t="s">
         <v>2280</v>
       </c>
@@ -33206,8 +34489,11 @@
       <c r="R429" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="430" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S429" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="430" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A430" s="1" t="s">
         <v>2283</v>
       </c>
@@ -33262,8 +34548,11 @@
       <c r="R430" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="431" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S430" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="431" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A431" s="1" t="s">
         <v>2287</v>
       </c>
@@ -33318,8 +34607,11 @@
       <c r="R431" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="432" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S431" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="432" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A432" s="1" t="s">
         <v>2293</v>
       </c>
@@ -33374,8 +34666,11 @@
       <c r="R432" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="433" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S432" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="433" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A433" s="1" t="s">
         <v>2297</v>
       </c>
@@ -33430,8 +34725,11 @@
       <c r="R433" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="434" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S433" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="434" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A434" s="1" t="s">
         <v>2301</v>
       </c>
@@ -33486,8 +34784,11 @@
       <c r="R434" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="435" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S434" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="435" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A435" s="1" t="s">
         <v>2305</v>
       </c>
@@ -33542,8 +34843,11 @@
       <c r="R435" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="436" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S435" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="436" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A436" s="1" t="s">
         <v>2309</v>
       </c>
@@ -33598,8 +34902,11 @@
       <c r="R436" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="437" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S436" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="437" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A437" s="1" t="s">
         <v>2313</v>
       </c>
@@ -33654,8 +34961,11 @@
       <c r="R437" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="438" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S437" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="438" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A438" s="1" t="s">
         <v>2316</v>
       </c>
@@ -33710,8 +35020,11 @@
       <c r="R438" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="439" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S438" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="439" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A439" s="1" t="s">
         <v>2320</v>
       </c>
@@ -33766,8 +35079,11 @@
       <c r="R439" s="1" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="440" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S439" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="440" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A440" s="1" t="s">
         <v>2323</v>
       </c>
@@ -33822,13 +35138,12 @@
       <c r="R440" s="1" t="s">
         <v>2597</v>
       </c>
+      <c r="S440" s="1" t="s">
+        <v>2597</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1" xr:uid="{8A57DF34-4FD0-476A-ABD4-C75283F5DBFA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R440">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:S1" xr:uid="{8A57DF34-4FD0-476A-ABD4-C75283F5DBFA}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -33836,22 +35151,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}">
-  <dimension ref="A1:T142"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:U440"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="9.85546875" customWidth="1"/>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="31.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.85546875" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="17" width="9.85546875" customWidth="1"/>
-    <col min="18" max="30" width="14.85546875" customWidth="1"/>
+    <col min="1" max="2" width="9.81640625" customWidth="1"/>
+    <col min="3" max="3" width="14.1796875" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="31.453125" customWidth="1"/>
+    <col min="6" max="6" width="17.26953125" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.81640625" customWidth="1"/>
+    <col min="9" max="9" width="16.453125" customWidth="1"/>
+    <col min="10" max="17" width="9.81640625" customWidth="1"/>
+    <col min="18" max="30" width="14.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>300</v>
       </c>
@@ -33912,8 +35227,11 @@
       <c r="T1" s="1" t="s">
         <v>2687</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U1" s="1" t="s">
+        <v>2750</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -33974,8 +35292,11 @@
       <c r="T2" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U2" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -34027,8 +35348,20 @@
       <c r="Q3" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="R3" t="s">
+        <v>2597</v>
+      </c>
+      <c r="S3" t="s">
+        <v>2597</v>
+      </c>
+      <c r="T3" t="s">
+        <v>2597</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -34089,8 +35422,11 @@
       <c r="T4" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U4" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>54</v>
       </c>
@@ -34151,8 +35487,11 @@
       <c r="T5" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U5" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>56</v>
       </c>
@@ -34213,8 +35552,11 @@
       <c r="T6" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="U6" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -34275,8 +35617,11 @@
       <c r="T7" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U7" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -34337,8 +35682,11 @@
       <c r="T8" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U8" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -34399,8 +35747,11 @@
       <c r="T9" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U9" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>65</v>
       </c>
@@ -34461,8 +35812,11 @@
       <c r="T10" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U10" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -34523,8 +35877,11 @@
       <c r="T11" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U11" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>70</v>
       </c>
@@ -34585,8 +35942,11 @@
       <c r="T12" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U12" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -34647,8 +36007,11 @@
       <c r="T13" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U13" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>73</v>
       </c>
@@ -34709,8 +36072,11 @@
       <c r="T14" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U14" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -34771,8 +36137,11 @@
       <c r="T15" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U15" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>79</v>
       </c>
@@ -34833,8 +36202,11 @@
       <c r="T16" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U16" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>81</v>
       </c>
@@ -34895,8 +36267,11 @@
       <c r="T17" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U17" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>84</v>
       </c>
@@ -34957,8 +36332,11 @@
       <c r="T18" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U18" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>85</v>
       </c>
@@ -35019,8 +36397,11 @@
       <c r="T19" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U19" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>88</v>
       </c>
@@ -35081,8 +36462,11 @@
       <c r="T20" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U20" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>90</v>
       </c>
@@ -35143,8 +36527,11 @@
       <c r="T21" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U21" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -35205,8 +36592,11 @@
       <c r="T22" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U22" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -35267,8 +36657,11 @@
       <c r="T23" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U23" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>96</v>
       </c>
@@ -35329,8 +36722,11 @@
       <c r="T24" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U24" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>99</v>
       </c>
@@ -35391,8 +36787,11 @@
       <c r="T25" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U25" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>100</v>
       </c>
@@ -35453,8 +36852,11 @@
       <c r="T26" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U26" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -35515,8 +36917,11 @@
       <c r="T27" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U27" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>106</v>
       </c>
@@ -35577,8 +36982,11 @@
       <c r="T28" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U28" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>109</v>
       </c>
@@ -35639,8 +37047,11 @@
       <c r="T29" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U29" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>111</v>
       </c>
@@ -35701,8 +37112,11 @@
       <c r="T30" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U30" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>111</v>
       </c>
@@ -35763,8 +37177,11 @@
       <c r="T31" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U31" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>112</v>
       </c>
@@ -35825,8 +37242,11 @@
       <c r="T32" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U32" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>114</v>
       </c>
@@ -35887,8 +37307,11 @@
       <c r="T33" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U33" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -35949,8 +37372,11 @@
       <c r="T34" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U34" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>118</v>
       </c>
@@ -36011,8 +37437,11 @@
       <c r="T35" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U35" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>121</v>
       </c>
@@ -36073,8 +37502,11 @@
       <c r="T36" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U36" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>124</v>
       </c>
@@ -36135,8 +37567,11 @@
       <c r="T37" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U37" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>125</v>
       </c>
@@ -36197,8 +37632,11 @@
       <c r="T38" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U38" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>126</v>
       </c>
@@ -36259,8 +37697,11 @@
       <c r="T39" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U39" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>129</v>
       </c>
@@ -36321,8 +37762,11 @@
       <c r="T40" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U40" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>132</v>
       </c>
@@ -36383,8 +37827,11 @@
       <c r="T41" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U41" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>133</v>
       </c>
@@ -36445,8 +37892,11 @@
       <c r="T42" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U42" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>134</v>
       </c>
@@ -36507,8 +37957,11 @@
       <c r="T43" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U43" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>135</v>
       </c>
@@ -36569,8 +38022,11 @@
       <c r="T44" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U44" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>137</v>
       </c>
@@ -36631,8 +38087,11 @@
       <c r="T45" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U45" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>138</v>
       </c>
@@ -36693,8 +38152,11 @@
       <c r="T46" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U46" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>140</v>
       </c>
@@ -36755,8 +38217,11 @@
       <c r="T47" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U47" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>143</v>
       </c>
@@ -36817,8 +38282,11 @@
       <c r="T48" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U48" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>146</v>
       </c>
@@ -36879,8 +38347,11 @@
       <c r="T49" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U49" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>148</v>
       </c>
@@ -36941,8 +38412,11 @@
       <c r="T50" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U50" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -37003,8 +38477,11 @@
       <c r="T51" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U51" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -37065,8 +38542,11 @@
       <c r="T52" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U52" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>155</v>
       </c>
@@ -37127,8 +38607,11 @@
       <c r="T53" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U53" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>156</v>
       </c>
@@ -37189,8 +38672,11 @@
       <c r="T54" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U54" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>2653</v>
       </c>
@@ -37251,8 +38737,11 @@
       <c r="T55" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U55" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>2655</v>
       </c>
@@ -37313,8 +38802,11 @@
       <c r="T56" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U56" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>2654</v>
       </c>
@@ -37375,8 +38867,11 @@
       <c r="T57" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U57" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>2659</v>
       </c>
@@ -37437,8 +38932,11 @@
       <c r="T58" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U58" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>158</v>
       </c>
@@ -37499,8 +38997,11 @@
       <c r="T59" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U59" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>160</v>
       </c>
@@ -37561,8 +39062,11 @@
       <c r="T60" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U60" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>162</v>
       </c>
@@ -37623,8 +39127,11 @@
       <c r="T61" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U61" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>163</v>
       </c>
@@ -37685,8 +39192,11 @@
       <c r="T62" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U62" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>165</v>
       </c>
@@ -37747,8 +39257,11 @@
       <c r="T63" t="s">
         <v>2746</v>
       </c>
-    </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U63" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>168</v>
       </c>
@@ -37809,8 +39322,11 @@
       <c r="T64" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U64" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>169</v>
       </c>
@@ -37871,8 +39387,11 @@
       <c r="T65" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U65" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>171</v>
       </c>
@@ -37933,8 +39452,11 @@
       <c r="T66" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U66" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>174</v>
       </c>
@@ -37995,8 +39517,11 @@
       <c r="T67" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U67" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>177</v>
       </c>
@@ -38057,8 +39582,11 @@
       <c r="T68" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="69" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U68" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>179</v>
       </c>
@@ -38119,8 +39647,11 @@
       <c r="T69" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U69" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>180</v>
       </c>
@@ -38181,8 +39712,11 @@
       <c r="T70" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U70" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>183</v>
       </c>
@@ -38243,8 +39777,11 @@
       <c r="T71" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U71" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>185</v>
       </c>
@@ -38305,8 +39842,11 @@
       <c r="T72" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U72" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>186</v>
       </c>
@@ -38367,8 +39907,11 @@
       <c r="T73" t="s">
         <v>2746</v>
       </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U73" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>189</v>
       </c>
@@ -38429,8 +39972,11 @@
       <c r="T74" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U74" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>190</v>
       </c>
@@ -38491,8 +40037,11 @@
       <c r="T75" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U75" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>191</v>
       </c>
@@ -38553,8 +40102,11 @@
       <c r="T76" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U76" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>192</v>
       </c>
@@ -38615,8 +40167,11 @@
       <c r="T77" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U77" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>194</v>
       </c>
@@ -38677,8 +40232,11 @@
       <c r="T78" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U78" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>195</v>
       </c>
@@ -38739,8 +40297,11 @@
       <c r="T79" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="80" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U79" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>197</v>
       </c>
@@ -38801,8 +40362,11 @@
       <c r="T80" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="81" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U80" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>199</v>
       </c>
@@ -38863,8 +40427,11 @@
       <c r="T81" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="82" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U81" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>201</v>
       </c>
@@ -38925,8 +40492,11 @@
       <c r="T82" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="83" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U82" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>203</v>
       </c>
@@ -38987,8 +40557,11 @@
       <c r="T83" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="84" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U83" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>204</v>
       </c>
@@ -39049,8 +40622,11 @@
       <c r="T84" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="85" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U84" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>206</v>
       </c>
@@ -39111,8 +40687,11 @@
       <c r="T85" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="86" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U85" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>208</v>
       </c>
@@ -39173,8 +40752,11 @@
       <c r="T86" t="s">
         <v>2746</v>
       </c>
-    </row>
-    <row r="87" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U86" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>210</v>
       </c>
@@ -39235,8 +40817,11 @@
       <c r="T87" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="88" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U87" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>212</v>
       </c>
@@ -39297,8 +40882,11 @@
       <c r="T88" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="89" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U88" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>213</v>
       </c>
@@ -39359,8 +40947,11 @@
       <c r="T89" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="90" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U89" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>214</v>
       </c>
@@ -39421,8 +41012,11 @@
       <c r="T90" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="91" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U90" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>216</v>
       </c>
@@ -39483,8 +41077,11 @@
       <c r="T91" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="92" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U91" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>217</v>
       </c>
@@ -39545,8 +41142,11 @@
       <c r="T92" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="93" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U92" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>218</v>
       </c>
@@ -39607,8 +41207,11 @@
       <c r="T93" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="94" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U93" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>219</v>
       </c>
@@ -39669,8 +41272,11 @@
       <c r="T94" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="95" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U94" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>220</v>
       </c>
@@ -39731,8 +41337,11 @@
       <c r="T95" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="96" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U95" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>221</v>
       </c>
@@ -39793,8 +41402,11 @@
       <c r="T96" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="97" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U96" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>222</v>
       </c>
@@ -39855,8 +41467,11 @@
       <c r="T97" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="98" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U97" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>223</v>
       </c>
@@ -39917,8 +41532,11 @@
       <c r="T98" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="99" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U98" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>224</v>
       </c>
@@ -39979,8 +41597,11 @@
       <c r="T99" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="100" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U99" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>225</v>
       </c>
@@ -40041,8 +41662,11 @@
       <c r="T100" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="101" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U100" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>227</v>
       </c>
@@ -40103,8 +41727,11 @@
       <c r="T101" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="102" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U101" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>229</v>
       </c>
@@ -40165,8 +41792,11 @@
       <c r="T102" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="103" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U102" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>232</v>
       </c>
@@ -40227,8 +41857,11 @@
       <c r="T103" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="104" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U103" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>234</v>
       </c>
@@ -40289,8 +41922,11 @@
       <c r="T104" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="105" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U104" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>236</v>
       </c>
@@ -40351,8 +41987,11 @@
       <c r="T105" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="106" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U105" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>237</v>
       </c>
@@ -40413,8 +42052,11 @@
       <c r="T106" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="107" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U106" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>239</v>
       </c>
@@ -40475,8 +42117,11 @@
       <c r="T107" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="108" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U107" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="108" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>241</v>
       </c>
@@ -40537,8 +42182,11 @@
       <c r="T108" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="109" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U108" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="109" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>243</v>
       </c>
@@ -40599,8 +42247,11 @@
       <c r="T109" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="110" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U109" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>244</v>
       </c>
@@ -40661,8 +42312,11 @@
       <c r="T110" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="111" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U110" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>245</v>
       </c>
@@ -40723,8 +42377,11 @@
       <c r="T111" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="112" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U111" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>247</v>
       </c>
@@ -40785,8 +42442,11 @@
       <c r="T112" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="113" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U112" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>248</v>
       </c>
@@ -40847,8 +42507,11 @@
       <c r="T113" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="114" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U113" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>250</v>
       </c>
@@ -40909,8 +42572,11 @@
       <c r="T114" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="115" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U114" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>251</v>
       </c>
@@ -40971,8 +42637,11 @@
       <c r="T115" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="116" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U115" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>253</v>
       </c>
@@ -41033,8 +42702,11 @@
       <c r="T116" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="117" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U116" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>254</v>
       </c>
@@ -41095,8 +42767,11 @@
       <c r="T117" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="118" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U117" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>256</v>
       </c>
@@ -41157,8 +42832,11 @@
       <c r="T118" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="119" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U118" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>259</v>
       </c>
@@ -41219,8 +42897,11 @@
       <c r="T119" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="120" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U119" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>262</v>
       </c>
@@ -41281,8 +42962,11 @@
       <c r="T120" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="121" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U120" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>263</v>
       </c>
@@ -41343,8 +43027,11 @@
       <c r="T121" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="122" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U121" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>265</v>
       </c>
@@ -41405,8 +43092,11 @@
       <c r="T122" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="123" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U122" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>266</v>
       </c>
@@ -41467,8 +43157,11 @@
       <c r="T123" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="124" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U123" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>268</v>
       </c>
@@ -41529,8 +43222,11 @@
       <c r="T124" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="125" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U124" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>271</v>
       </c>
@@ -41591,8 +43287,11 @@
       <c r="T125" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="126" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U125" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>272</v>
       </c>
@@ -41653,8 +43352,11 @@
       <c r="T126" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="127" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U126" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>273</v>
       </c>
@@ -41715,8 +43417,11 @@
       <c r="T127" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="128" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U127" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>275</v>
       </c>
@@ -41777,8 +43482,11 @@
       <c r="T128" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="129" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U128" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>278</v>
       </c>
@@ -41839,8 +43547,11 @@
       <c r="T129" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="130" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U129" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>279</v>
       </c>
@@ -41901,8 +43612,11 @@
       <c r="T130" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="131" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U130" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>282</v>
       </c>
@@ -41963,8 +43677,11 @@
       <c r="T131" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="132" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U131" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>285</v>
       </c>
@@ -42025,8 +43742,11 @@
       <c r="T132" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="133" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U132" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>288</v>
       </c>
@@ -42084,8 +43804,11 @@
       <c r="T133" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="134" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U133" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>2586</v>
       </c>
@@ -42146,8 +43869,11 @@
       <c r="T134" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="135" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U134" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>2585</v>
       </c>
@@ -42208,8 +43934,11 @@
       <c r="T135" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="136" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U135" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>2583</v>
       </c>
@@ -42270,8 +43999,11 @@
       <c r="T136" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="137" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U136" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>289</v>
       </c>
@@ -42332,8 +44064,11 @@
       <c r="T137" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="138" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U137" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>291</v>
       </c>
@@ -42394,8 +44129,11 @@
       <c r="T138" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="139" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U138" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>294</v>
       </c>
@@ -42456,8 +44194,11 @@
       <c r="T139" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="140" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U139" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>295</v>
       </c>
@@ -42518,8 +44259,11 @@
       <c r="T140" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="141" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U140" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>298</v>
       </c>
@@ -42580,8 +44324,11 @@
       <c r="T141" t="s">
         <v>2597</v>
       </c>
-    </row>
-    <row r="142" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U141" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>2524</v>
       </c>
@@ -42642,13 +44389,1502 @@
       <c r="T142" t="s">
         <v>2597</v>
       </c>
+      <c r="U142" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U143" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="U144" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="145" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U145" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="146" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U146" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="147" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U147" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="148" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U148" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="149" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U149" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="150" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U150" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="151" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U151" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="152" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U152" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="153" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U153" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="154" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U154" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="155" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U155" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="156" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U156" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="157" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U157" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="158" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U158" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="159" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U159" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="160" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U160" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="161" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U161" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="162" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U162" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="163" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U163" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="164" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U164" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="165" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U165" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="166" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U166" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="167" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U167" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="168" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U168" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="169" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U169" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="170" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U170" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="171" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U171" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="172" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U172" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="173" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U173" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="174" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U174" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="175" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U175" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="176" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U176" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="177" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U177" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="178" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U178" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="179" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U179" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="180" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U180" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="181" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U181" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="182" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U182" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="183" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U183" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="184" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U184" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="185" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U185" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="186" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U186" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="187" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U187" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="188" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U188" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="189" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U189" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="190" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U190" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="191" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U191" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="192" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U192" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="193" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U193" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="194" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U194" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="195" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U195" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="196" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U196" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="197" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U197" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="198" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U198" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="199" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U199" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="200" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U200" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="201" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U201" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="202" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U202" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="203" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U203" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="204" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U204" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="205" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U205" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="206" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U206" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="207" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U207" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="208" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U208" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="209" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U209" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="210" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U210" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="211" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U211" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="212" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U212" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="213" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U213" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="214" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U214" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="215" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U215" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="216" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U216" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="217" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U217" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="218" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U218" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="219" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U219" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="220" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U220" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="221" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U221" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="222" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U222" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="223" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U223" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="224" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U224" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="225" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U225" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="226" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U226" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="227" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U227" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="228" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U228" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="229" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U229" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="230" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U230" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="231" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U231" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="232" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U232" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="233" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U233" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="234" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U234" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="235" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U235" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="236" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U236" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="237" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U237" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="238" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U238" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="239" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U239" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="240" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U240" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="241" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U241" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="242" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U242" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="243" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U243" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="244" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U244" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="245" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U245" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="246" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U246" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="247" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U247" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="248" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U248" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="249" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U249" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="250" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U250" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="251" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U251" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="252" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U252" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="253" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U253" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="254" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U254" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="255" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U255" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="256" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U256" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="257" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U257" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="258" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U258" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="259" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U259" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="260" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U260" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="261" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U261" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="262" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U262" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="263" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U263" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="264" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U264" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="265" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U265" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="266" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U266" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="267" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U267" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="268" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U268" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="269" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U269" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="270" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U270" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="271" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U271" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="272" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U272" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="273" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U273" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="274" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U274" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="275" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U275" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="276" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U276" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="277" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U277" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="278" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U278" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="279" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U279" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="280" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U280" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="281" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U281" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="282" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U282" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="283" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U283" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="284" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U284" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="285" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U285" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="286" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U286" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="287" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U287" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="288" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U288" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="289" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U289" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="290" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U290" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="291" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U291" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="292" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U292" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="293" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U293" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="294" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U294" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="295" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U295" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="296" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U296" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="297" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U297" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="298" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U298" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="299" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U299" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="300" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U300" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="301" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U301" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="302" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U302" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="303" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U303" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="304" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U304" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="305" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U305" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="306" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U306" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="307" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U307" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="308" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U308" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="309" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U309" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="310" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U310" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="311" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U311" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="312" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U312" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="313" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U313" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="314" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U314" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="315" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U315" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="316" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U316" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="317" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U317" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="318" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U318" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="319" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U319" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="320" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U320" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="321" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U321" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="322" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U322" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="323" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U323" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="324" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U324" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="325" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U325" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="326" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U326" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="327" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U327" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="328" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U328" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="329" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U329" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="330" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U330" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="331" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U331" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="332" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U332" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="333" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U333" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="334" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U334" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="335" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U335" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="336" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U336" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="337" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U337" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="338" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U338" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="339" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U339" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="340" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U340" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="341" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U341" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="342" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U342" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="343" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U343" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="344" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U344" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="345" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U345" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="346" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U346" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="347" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U347" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="348" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U348" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="349" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U349" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="350" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U350" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="351" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U351" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="352" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U352" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="353" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U353" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="354" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U354" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="355" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U355" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="356" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U356" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="357" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U357" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="358" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U358" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="359" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U359" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="360" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U360" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="361" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U361" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="362" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U362" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="363" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U363" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="364" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U364" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="365" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U365" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="366" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U366" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="367" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U367" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="368" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U368" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="369" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U369" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="370" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U370" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="371" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U371" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="372" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U372" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="373" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U373" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="374" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U374" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="375" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U375" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="376" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U376" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="377" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U377" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="378" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U378" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="379" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U379" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="380" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U380" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="381" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U381" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="382" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U382" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="383" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U383" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="384" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U384" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="385" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U385" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="386" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U386" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="387" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U387" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="388" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U388" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="389" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U389" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="390" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U390" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="391" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U391" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="392" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U392" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="393" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U393" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="394" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U394" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="395" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U395" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="396" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U396" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="397" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U397" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="398" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U398" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="399" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U399" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="400" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U400" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="401" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U401" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="402" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U402" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="403" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U403" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="404" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U404" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="405" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U405" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="406" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U406" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="407" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U407" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="408" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U408" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="409" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U409" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="410" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U410" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="411" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U411" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="412" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U412" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="413" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U413" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="414" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U414" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="415" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U415" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="416" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U416" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="417" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U417" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="418" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U418" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="419" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U419" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="420" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U420" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="421" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U421" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="422" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U422" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="423" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U423" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="424" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U424" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="425" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U425" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="426" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U426" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="427" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U427" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="428" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U428" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="429" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U429" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="430" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U430" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="431" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U431" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="432" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U432" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="433" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U433" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="434" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U434" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="435" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U435" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="436" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U436" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="437" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U437" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="438" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U438" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="439" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U439" s="1" t="s">
+        <v>2597</v>
+      </c>
+    </row>
+    <row r="440" spans="21:21" x14ac:dyDescent="0.35">
+      <c r="U440" s="1" t="s">
+        <v>2597</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T1" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:T142">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="A1:U1" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/cirt_data.xlsx
+++ b/cirt_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://o365coloradoedu-my.sharepoint.com/personal/daad2295_colorado_edu/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="8_{9DEE3B3B-C278-45E7-AFEB-FC7D865F8C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F94D6800-BE81-42EB-8111-3F4D9F2E7C98}"/>
+  <xr:revisionPtr revIDLastSave="198" documentId="8_{9DEE3B3B-C278-45E7-AFEB-FC7D865F8C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{615EC137-2975-4E2A-B918-6E1966ADF36F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{969D6A76-162A-4286-A653-6BBA36AECB0D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{969D6A76-162A-4286-A653-6BBA36AECB0D}"/>
   </bookViews>
   <sheets>
     <sheet name="courses" sheetId="1" r:id="rId1"/>
@@ -8878,6 +8878,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -35183,7 +35187,8 @@
   <dimension ref="A1:U604"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="14.140625" customWidth="1"/>
     <col min="4" max="4" width="9.85546875" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.42578125" customWidth="1"/>
@@ -35310,19 +35315,19 @@
         <v>2323</v>
       </c>
       <c r="Q2" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R2" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S2" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T2" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U2" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
@@ -35378,16 +35383,16 @@
         <v>50</v>
       </c>
       <c r="R3" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S3" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T3" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U3" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U3" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
@@ -35440,19 +35445,19 @@
         <v>2335</v>
       </c>
       <c r="Q4" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R4" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S4" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T4" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U4" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -35505,19 +35510,19 @@
         <v>2323</v>
       </c>
       <c r="Q5" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R5" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S5" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T5" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U5" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U5" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -35570,19 +35575,19 @@
         <v>2323</v>
       </c>
       <c r="Q6" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R6" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S6" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T6" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U6" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="15.75" x14ac:dyDescent="0.3">
@@ -35638,16 +35643,16 @@
         <v>59</v>
       </c>
       <c r="R7" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S7" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T7" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U7" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
@@ -35700,19 +35705,19 @@
         <v>2323</v>
       </c>
       <c r="Q8" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R8" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S8" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T8" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U8" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
@@ -35765,19 +35770,19 @@
         <v>2323</v>
       </c>
       <c r="Q9" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R9" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S9" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T9" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U9" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
@@ -35830,19 +35835,19 @@
         <v>2323</v>
       </c>
       <c r="Q10" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R10" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S10" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T10" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U10" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
@@ -35895,19 +35900,19 @@
         <v>2323</v>
       </c>
       <c r="Q11" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R11" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S11" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T11" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U11" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
@@ -35960,19 +35965,19 @@
         <v>2323</v>
       </c>
       <c r="Q12" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R12" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S12" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T12" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U12" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -36025,19 +36030,19 @@
         <v>2323</v>
       </c>
       <c r="Q13" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R13" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S13" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T13" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U13" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U13" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -36090,19 +36095,19 @@
         <v>2323</v>
       </c>
       <c r="Q14" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R14" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S14" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T14" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U14" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
@@ -36158,16 +36163,16 @@
         <v>77</v>
       </c>
       <c r="R15" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S15" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T15" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U15" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -36220,19 +36225,19 @@
         <v>2323</v>
       </c>
       <c r="Q16" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R16" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S16" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T16" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U16" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
@@ -36285,19 +36290,19 @@
         <v>2323</v>
       </c>
       <c r="Q17" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R17" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S17" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T17" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U17" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
@@ -36350,19 +36355,19 @@
         <v>2323</v>
       </c>
       <c r="Q18" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R18" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S18" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T18" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U18" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
@@ -36415,19 +36420,19 @@
         <v>2335</v>
       </c>
       <c r="Q19" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R19" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S19" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T19" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U19" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -36480,19 +36485,19 @@
         <v>2335</v>
       </c>
       <c r="Q20" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R20" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S20" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T20" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U20" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -36545,19 +36550,19 @@
         <v>2335</v>
       </c>
       <c r="Q21" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R21" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S21" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T21" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U21" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -36610,19 +36615,19 @@
         <v>2335</v>
       </c>
       <c r="Q22" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R22" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S22" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T22" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U22" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
@@ -36675,19 +36680,19 @@
         <v>2349</v>
       </c>
       <c r="Q23" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R23" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S23" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T23" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U23" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -36740,19 +36745,19 @@
         <v>2323</v>
       </c>
       <c r="Q24" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R24" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S24" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T24" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U24" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
@@ -36808,16 +36813,16 @@
         <v>59</v>
       </c>
       <c r="R25" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S25" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T25" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U25" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -36870,19 +36875,19 @@
         <v>2323</v>
       </c>
       <c r="Q26" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R26" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S26" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T26" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U26" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -36935,19 +36940,19 @@
         <v>2323</v>
       </c>
       <c r="Q27" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R27" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S27" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T27" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U27" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -37000,19 +37005,19 @@
         <v>2323</v>
       </c>
       <c r="Q28" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R28" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S28" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T28" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U28" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -37068,16 +37073,16 @@
         <v>59</v>
       </c>
       <c r="R29" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S29" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T29" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U29" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -37130,19 +37135,19 @@
         <v>2323</v>
       </c>
       <c r="Q30" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R30" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S30" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T30" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U30" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -37195,19 +37200,19 @@
         <v>2323</v>
       </c>
       <c r="Q31" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R31" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S31" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T31" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U31" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -37260,19 +37265,19 @@
         <v>2335</v>
       </c>
       <c r="Q32" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R32" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S32" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T32" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U32" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -37325,19 +37330,19 @@
         <v>2335</v>
       </c>
       <c r="Q33" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R33" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S33" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T33" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U33" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
@@ -37390,19 +37395,19 @@
         <v>2335</v>
       </c>
       <c r="Q34" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R34" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S34" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T34" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U34" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -37455,19 +37460,19 @@
         <v>2335</v>
       </c>
       <c r="Q35" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R35" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S35" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T35" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U35" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -37520,19 +37525,19 @@
         <v>2335</v>
       </c>
       <c r="Q36" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R36" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S36" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T36" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U36" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -37588,16 +37593,16 @@
         <v>59</v>
       </c>
       <c r="R37" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S37" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T37" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U37" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -37650,19 +37655,19 @@
         <v>2323</v>
       </c>
       <c r="Q38" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R38" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S38" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T38" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U38" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -37715,19 +37720,19 @@
         <v>2323</v>
       </c>
       <c r="Q39" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R39" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S39" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T39" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U39" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -37783,16 +37788,16 @@
         <v>130</v>
       </c>
       <c r="R40" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S40" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T40" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U40" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -37845,19 +37850,19 @@
         <v>2323</v>
       </c>
       <c r="Q41" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R41" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S41" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T41" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U41" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -37910,19 +37915,19 @@
         <v>2335</v>
       </c>
       <c r="Q42" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R42" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S42" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T42" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U42" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -37978,16 +37983,16 @@
         <v>130</v>
       </c>
       <c r="R43" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S43" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T43" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U43" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -38040,19 +38045,19 @@
         <v>2323</v>
       </c>
       <c r="Q44" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R44" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S44" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T44" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U44" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -38105,19 +38110,19 @@
         <v>2335</v>
       </c>
       <c r="Q45" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R45" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S45" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T45" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U45" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -38173,16 +38178,16 @@
         <v>130</v>
       </c>
       <c r="R46" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S46" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T46" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U46" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -38235,19 +38240,19 @@
         <v>2335</v>
       </c>
       <c r="Q47" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R47" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S47" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T47" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U47" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -38300,19 +38305,19 @@
         <v>2323</v>
       </c>
       <c r="Q48" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R48" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S48" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T48" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U48" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U48" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -38365,19 +38370,19 @@
         <v>2349</v>
       </c>
       <c r="Q49" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R49" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S49" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T49" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U49" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U49" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -38430,19 +38435,19 @@
         <v>2335</v>
       </c>
       <c r="Q50" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R50" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S50" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T50" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U50" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U50" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -38495,19 +38500,19 @@
         <v>2323</v>
       </c>
       <c r="Q51" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R51" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S51" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T51" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U51" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
@@ -38560,19 +38565,19 @@
         <v>2323</v>
       </c>
       <c r="Q52" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R52" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S52" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T52" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U52" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -38625,19 +38630,19 @@
         <v>2323</v>
       </c>
       <c r="Q53" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R53" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S53" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T53" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U53" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -38690,19 +38695,19 @@
         <v>2335</v>
       </c>
       <c r="Q54" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R54" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S54" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T54" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U54" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
@@ -38758,16 +38763,16 @@
         <v>59</v>
       </c>
       <c r="R55" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S55" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T55" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U55" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
@@ -38820,19 +38825,19 @@
         <v>2323</v>
       </c>
       <c r="Q56" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R56" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S56" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T56" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U56" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -38888,16 +38893,16 @@
         <v>59</v>
       </c>
       <c r="R57" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S57" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T57" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U57" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -38950,19 +38955,19 @@
         <v>2323</v>
       </c>
       <c r="Q58" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R58" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S58" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T58" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U58" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U58" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -39015,19 +39020,19 @@
         <v>2323</v>
       </c>
       <c r="Q59" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R59" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S59" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T59" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U59" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U59" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -39080,19 +39085,19 @@
         <v>2323</v>
       </c>
       <c r="Q60" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R60" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S60" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T60" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U60" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U60" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -39145,19 +39150,19 @@
         <v>2350</v>
       </c>
       <c r="Q61" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R61" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S61" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T61" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U61" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U61" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
@@ -39210,19 +39215,19 @@
         <v>2350</v>
       </c>
       <c r="Q62" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R62" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S62" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T62" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U62" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U62" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
@@ -39275,7 +39280,7 @@
         <v>2348</v>
       </c>
       <c r="Q63" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R63" t="s">
         <v>2643</v>
@@ -39286,8 +39291,8 @@
       <c r="T63" t="s">
         <v>2641</v>
       </c>
-      <c r="U63" s="1" t="s">
-        <v>2493</v>
+      <c r="U63" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
@@ -39340,19 +39345,19 @@
         <v>2323</v>
       </c>
       <c r="Q64" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R64" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S64" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T64" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U64" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U64" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
@@ -39405,19 +39410,19 @@
         <v>2323</v>
       </c>
       <c r="Q65" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R65" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S65" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T65" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U65" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U65" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
@@ -39470,19 +39475,19 @@
         <v>2323</v>
       </c>
       <c r="Q66" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R66" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S66" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T66" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U66" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
@@ -39538,16 +39543,16 @@
         <v>2545</v>
       </c>
       <c r="R67" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S67" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T67" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U67" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U67" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -39603,16 +39608,16 @@
         <v>2544</v>
       </c>
       <c r="R68" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S68" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T68" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U68" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U68" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
@@ -39665,19 +39670,19 @@
         <v>2323</v>
       </c>
       <c r="Q69" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R69" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S69" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T69" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U69" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
@@ -39730,19 +39735,19 @@
         <v>2335</v>
       </c>
       <c r="Q70" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R70" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S70" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T70" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U70" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U70" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
@@ -39795,19 +39800,19 @@
         <v>2323</v>
       </c>
       <c r="Q71" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R71" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S71" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T71" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U71" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U71" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
@@ -39860,19 +39865,19 @@
         <v>2350</v>
       </c>
       <c r="Q72" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R72" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S72" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T72" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U72" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U72" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
@@ -39925,7 +39930,7 @@
         <v>2323</v>
       </c>
       <c r="Q73" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R73" t="s">
         <v>2643</v>
@@ -39936,8 +39941,8 @@
       <c r="T73" t="s">
         <v>2641</v>
       </c>
-      <c r="U73" s="1" t="s">
-        <v>2493</v>
+      <c r="U73" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -39993,16 +39998,16 @@
         <v>2494</v>
       </c>
       <c r="R74" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S74" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T74" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U74" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U74" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
@@ -40055,19 +40060,19 @@
         <v>2323</v>
       </c>
       <c r="Q75" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R75" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S75" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T75" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U75" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U75" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
@@ -40120,19 +40125,19 @@
         <v>2323</v>
       </c>
       <c r="Q76" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R76" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S76" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T76" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U76" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U76" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
@@ -40185,19 +40190,19 @@
         <v>2323</v>
       </c>
       <c r="Q77" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R77" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S77" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T77" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U77" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U77" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
@@ -40253,16 +40258,16 @@
         <v>2494</v>
       </c>
       <c r="R78" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S78" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T78" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U78" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U78" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -40315,19 +40320,19 @@
         <v>2323</v>
       </c>
       <c r="Q79" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R79" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S79" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T79" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U79" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U79" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -40380,19 +40385,19 @@
         <v>2323</v>
       </c>
       <c r="Q80" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R80" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S80" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T80" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U80" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U80" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -40445,19 +40450,19 @@
         <v>2323</v>
       </c>
       <c r="Q81" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R81" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S81" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T81" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U81" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U81" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
@@ -40510,19 +40515,19 @@
         <v>2323</v>
       </c>
       <c r="Q82" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R82" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S82" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T82" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U82" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U82" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -40575,19 +40580,19 @@
         <v>2323</v>
       </c>
       <c r="Q83" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R83" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S83" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T83" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U83" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U83" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -40640,19 +40645,19 @@
         <v>2323</v>
       </c>
       <c r="Q84" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R84" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S84" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T84" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U84" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U84" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
@@ -40705,19 +40710,19 @@
         <v>2335</v>
       </c>
       <c r="Q85" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R85" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S85" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T85" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U85" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U85" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -40770,7 +40775,7 @@
         <v>2323</v>
       </c>
       <c r="Q86" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R86" t="s">
         <v>2643</v>
@@ -40781,8 +40786,8 @@
       <c r="T86" t="s">
         <v>2641</v>
       </c>
-      <c r="U86" s="1" t="s">
-        <v>2493</v>
+      <c r="U86" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -40838,16 +40843,16 @@
         <v>2544</v>
       </c>
       <c r="R87" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S87" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T87" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U87" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U87" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -40900,19 +40905,19 @@
         <v>2323</v>
       </c>
       <c r="Q88" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R88" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S88" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T88" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U88" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U88" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -40965,19 +40970,19 @@
         <v>2323</v>
       </c>
       <c r="Q89" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R89" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S89" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T89" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U89" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U89" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -41030,19 +41035,19 @@
         <v>2350</v>
       </c>
       <c r="Q90" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R90" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S90" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T90" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U90" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U90" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -41095,19 +41100,19 @@
         <v>2323</v>
       </c>
       <c r="Q91" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R91" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S91" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T91" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U91" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U91" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -41160,19 +41165,19 @@
         <v>2351</v>
       </c>
       <c r="Q92" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R92" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S92" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T92" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U92" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U92" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -41225,19 +41230,19 @@
         <v>2351</v>
       </c>
       <c r="Q93" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R93" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S93" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T93" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U93" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U93" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
@@ -41293,16 +41298,16 @@
         <v>2535</v>
       </c>
       <c r="R94" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S94" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T94" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U94" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U94" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
@@ -41355,19 +41360,19 @@
         <v>2323</v>
       </c>
       <c r="Q95" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R95" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S95" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T95" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U95" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U95" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
@@ -41420,19 +41425,19 @@
         <v>2323</v>
       </c>
       <c r="Q96" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R96" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S96" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T96" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U96" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U96" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
@@ -41485,19 +41490,19 @@
         <v>2323</v>
       </c>
       <c r="Q97" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R97" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S97" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T97" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U97" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U97" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -41550,19 +41555,19 @@
         <v>2323</v>
       </c>
       <c r="Q98" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R98" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S98" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T98" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U98" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U98" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -41615,19 +41620,19 @@
         <v>2323</v>
       </c>
       <c r="Q99" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R99" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S99" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T99" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U99" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U99" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -41683,16 +41688,16 @@
         <v>224</v>
       </c>
       <c r="R100" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S100" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T100" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U100" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U100" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -41745,19 +41750,19 @@
         <v>2323</v>
       </c>
       <c r="Q101" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R101" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S101" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T101" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U101" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U101" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
@@ -41810,19 +41815,19 @@
         <v>2351</v>
       </c>
       <c r="Q102" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R102" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S102" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T102" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U102" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U102" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
@@ -41875,19 +41880,19 @@
         <v>2335</v>
       </c>
       <c r="Q103" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R103" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S103" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T103" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U103" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U103" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -41940,19 +41945,19 @@
         <v>2323</v>
       </c>
       <c r="Q104" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R104" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S104" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T104" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U104" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U104" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -42005,19 +42010,19 @@
         <v>2335</v>
       </c>
       <c r="Q105" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R105" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S105" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T105" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U105" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U105" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -42073,16 +42078,16 @@
         <v>2494</v>
       </c>
       <c r="R106" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S106" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T106" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U106" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U106" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -42135,19 +42140,19 @@
         <v>2323</v>
       </c>
       <c r="Q107" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R107" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S107" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T107" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U107" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U107" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
@@ -42203,16 +42208,16 @@
         <v>2494</v>
       </c>
       <c r="R108" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S108" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T108" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U108" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U108" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -42265,19 +42270,19 @@
         <v>2323</v>
       </c>
       <c r="Q109" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R109" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S109" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T109" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U109" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U109" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -42330,19 +42335,19 @@
         <v>2323</v>
       </c>
       <c r="Q110" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R110" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S110" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T110" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U110" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U110" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -42395,19 +42400,19 @@
         <v>2323</v>
       </c>
       <c r="Q111" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R111" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S111" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T111" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U111" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U111" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -42463,16 +42468,16 @@
         <v>2494</v>
       </c>
       <c r="R112" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S112" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T112" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U112" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U112" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -42525,19 +42530,19 @@
         <v>2323</v>
       </c>
       <c r="Q113" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R113" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S113" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T113" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U113" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U113" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
@@ -42590,19 +42595,19 @@
         <v>2323</v>
       </c>
       <c r="Q114" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R114" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S114" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T114" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U114" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U114" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -42655,19 +42660,19 @@
         <v>2323</v>
       </c>
       <c r="Q115" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R115" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S115" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T115" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U115" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U115" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -42720,19 +42725,19 @@
         <v>2323</v>
       </c>
       <c r="Q116" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R116" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S116" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T116" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U116" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U116" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -42785,19 +42790,19 @@
         <v>2323</v>
       </c>
       <c r="Q117" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R117" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S117" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T117" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U117" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U117" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -42850,19 +42855,19 @@
         <v>2323</v>
       </c>
       <c r="Q118" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R118" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S118" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T118" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U118" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U118" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -42915,19 +42920,19 @@
         <v>2335</v>
       </c>
       <c r="Q119" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R119" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S119" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T119" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U119" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U119" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
@@ -42980,19 +42985,19 @@
         <v>2335</v>
       </c>
       <c r="Q120" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R120" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S120" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T120" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U120" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U120" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
@@ -43045,19 +43050,19 @@
         <v>2323</v>
       </c>
       <c r="Q121" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R121" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S121" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T121" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U121" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U121" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
@@ -43113,16 +43118,16 @@
         <v>2230</v>
       </c>
       <c r="R122" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S122" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T122" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U122" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U122" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
@@ -43175,19 +43180,19 @@
         <v>2351</v>
       </c>
       <c r="Q123" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R123" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S123" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T123" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U123" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U123" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
@@ -43240,19 +43245,19 @@
         <v>2323</v>
       </c>
       <c r="Q124" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R124" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S124" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T124" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U124" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U124" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -43305,19 +43310,19 @@
         <v>2323</v>
       </c>
       <c r="Q125" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R125" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S125" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T125" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U125" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U125" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
@@ -43370,19 +43375,19 @@
         <v>2323</v>
       </c>
       <c r="Q126" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R126" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S126" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T126" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U126" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U126" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
@@ -43435,19 +43440,19 @@
         <v>2323</v>
       </c>
       <c r="Q127" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R127" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S127" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T127" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U127" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U127" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
@@ -43500,19 +43505,19 @@
         <v>2323</v>
       </c>
       <c r="Q128" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R128" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S128" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T128" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U128" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U128" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
@@ -43565,19 +43570,19 @@
         <v>2323</v>
       </c>
       <c r="Q129" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R129" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S129" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T129" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U129" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U129" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -43630,19 +43635,19 @@
         <v>2350</v>
       </c>
       <c r="Q130" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R130" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S130" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T130" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U130" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U130" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -43695,19 +43700,19 @@
         <v>2335</v>
       </c>
       <c r="Q131" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R131" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S131" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T131" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U131" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U131" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
@@ -43760,19 +43765,19 @@
         <v>2335</v>
       </c>
       <c r="Q132" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R132" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S132" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T132" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U132" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U132" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
@@ -43825,16 +43830,16 @@
         <v>2335</v>
       </c>
       <c r="R133" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S133" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T133" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U133" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U133" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
@@ -43887,19 +43892,19 @@
         <v>2323</v>
       </c>
       <c r="Q134" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R134" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S134" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T134" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U134" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U134" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
@@ -43952,19 +43957,19 @@
         <v>2323</v>
       </c>
       <c r="Q135" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R135" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S135" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T135" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U135" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U135" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -44017,19 +44022,19 @@
         <v>2323</v>
       </c>
       <c r="Q136" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R136" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S136" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T136" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U136" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U136" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
@@ -44082,19 +44087,19 @@
         <v>2335</v>
       </c>
       <c r="Q137" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R137" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S137" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T137" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U137" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U137" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
@@ -44150,16 +44155,16 @@
         <v>290</v>
       </c>
       <c r="R138" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S138" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T138" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U138" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U138" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
@@ -44215,16 +44220,16 @@
         <v>2534</v>
       </c>
       <c r="R139" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S139" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T139" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U139" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U139" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
@@ -44280,16 +44285,16 @@
         <v>294</v>
       </c>
       <c r="R140" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S140" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T140" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U140" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U140" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
@@ -44345,16 +44350,16 @@
         <v>2495</v>
       </c>
       <c r="R141" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S141" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T141" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U141" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U141" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
@@ -44407,19 +44412,19 @@
         <v>2323</v>
       </c>
       <c r="Q142" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="R142" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="S142" t="s">
-        <v>2493</v>
+        <v>2414</v>
       </c>
       <c r="T142" t="s">
-        <v>2493</v>
-      </c>
-      <c r="U142" s="1" t="s">
-        <v>2493</v>
+        <v>2414</v>
+      </c>
+      <c r="U142" t="s">
+        <v>2414</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -45809,13 +45814,14 @@
       <c r="U604" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U1" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}"/>
+  <autoFilter ref="A1:U1" xr:uid="{B785887B-576B-4D81-AE70-D107EA8277F5}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U142">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="D6" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
